--- a/research/traditional_assets/database/data/malawi/malawi_diversified.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_diversified.xlsx
@@ -1133,43 +1133,43 @@
         <v>9.802149532710279</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>963.562433164415</v>
       </c>
       <c r="G2">
         <v>0.407794676806084</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0205703422053232</v>
       </c>
       <c r="I2">
         <v>0.198243992606285</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>173.5</v>
       </c>
       <c r="L2">
-        <v>216.265000654143</v>
+        <v>214.099852903702</v>
       </c>
       <c r="M2">
         <v>-13</v>
       </c>
       <c r="N2">
-        <v>-13.1349993458574</v>
+        <v>-13.136147096298</v>
       </c>
       <c r="O2">
         <v>42.9</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.164</v>
       </c>
       <c r="Q2">
         <v>0.179649951491793</v>
       </c>
       <c r="R2">
-        <v>0.164868434277927</v>
+        <v>0.164744065843649</v>
       </c>
       <c r="S2">
         <v>0.132269088767667</v>
@@ -1191,13 +1191,13 @@
         <v>0.191365450113494</v>
       </c>
       <c r="X2">
-        <v>0.164868434277927</v>
+        <v>0.165950874589545</v>
       </c>
       <c r="Y2">
         <v>0.8902601722196271</v>
       </c>
       <c r="Z2">
-        <v>0.728207721842937</v>
+        <v>0.7348277920415091</v>
       </c>
       <c r="AA2">
         <v>42.9</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1648684342779272</v>
+        <v>0.1647440658436493</v>
       </c>
       <c r="C2">
-        <v>216.2650006541426</v>
+        <v>214.099852903702</v>
       </c>
       <c r="D2">
-        <v>-13.13499934585744</v>
+        <v>-13.13614709629804</v>
       </c>
       <c r="E2">
-        <v>-42.9</v>
+        <v>-40.736</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.164</v>
       </c>
       <c r="G2">
         <v>229.4</v>
@@ -1451,28 +1451,28 @@
         <v>104.883</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1088492</v>
       </c>
       <c r="N2">
-        <v>104.883</v>
+        <v>104.7741508</v>
       </c>
       <c r="O2">
-        <v>10.4883</v>
+        <v>10.47741508</v>
       </c>
       <c r="P2">
-        <v>94.3947</v>
+        <v>94.29673572000002</v>
       </c>
       <c r="Q2">
-        <v>94.71169999999999</v>
+        <v>94.61373572000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1648684342779272</v>
+        <v>0.1659508745895448</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7348277920415089</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>963.5624331644146</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1647440658436493</v>
+        <v>0.1646196974093714</v>
       </c>
       <c r="C3">
-        <v>214.099852903702</v>
+        <v>211.9347049526605</v>
       </c>
       <c r="D3">
-        <v>-13.13614709629804</v>
+        <v>-13.1372950473395</v>
       </c>
       <c r="E3">
-        <v>-40.736</v>
+        <v>-38.572</v>
       </c>
       <c r="F3">
-        <v>2.164</v>
+        <v>4.328</v>
       </c>
       <c r="G3">
         <v>229.4</v>
@@ -1533,28 +1533,28 @@
         <v>104.883</v>
       </c>
       <c r="M3">
-        <v>0.1088492</v>
+        <v>0.2176984</v>
       </c>
       <c r="N3">
-        <v>104.7741508</v>
+        <v>104.6653016</v>
       </c>
       <c r="O3">
-        <v>10.47741508</v>
+        <v>10.46653016</v>
       </c>
       <c r="P3">
-        <v>94.29673572000002</v>
+        <v>94.19877144</v>
       </c>
       <c r="Q3">
-        <v>94.61373572000001</v>
+        <v>94.51577143999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1659508745895448</v>
+        <v>0.1670554055197667</v>
       </c>
       <c r="T3">
-        <v>0.7348277920415089</v>
+        <v>0.7415829657135213</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>963.5624331644146</v>
+        <v>481.7812165822073</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1646196974093714</v>
+        <v>0.1644953289750935</v>
       </c>
       <c r="C4">
-        <v>211.9347049526605</v>
+        <v>209.7695568009656</v>
       </c>
       <c r="D4">
-        <v>-13.1372950473395</v>
+        <v>-13.13844319903444</v>
       </c>
       <c r="E4">
-        <v>-38.572</v>
+        <v>-36.408</v>
       </c>
       <c r="F4">
-        <v>4.328</v>
+        <v>6.492</v>
       </c>
       <c r="G4">
         <v>229.4</v>
@@ -1615,28 +1615,28 @@
         <v>104.883</v>
       </c>
       <c r="M4">
-        <v>0.2176984</v>
+        <v>0.3265476</v>
       </c>
       <c r="N4">
-        <v>104.6653016</v>
+        <v>104.5564524</v>
       </c>
       <c r="O4">
-        <v>10.46653016</v>
+        <v>10.45564524</v>
       </c>
       <c r="P4">
-        <v>94.19877144</v>
+        <v>94.10080716000002</v>
       </c>
       <c r="Q4">
-        <v>94.51577143999999</v>
+        <v>94.41780716000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1670554055197667</v>
+        <v>0.1681827102836015</v>
       </c>
       <c r="T4">
-        <v>0.7415829657135213</v>
+        <v>0.7484774213169154</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>481.7812165822073</v>
+        <v>321.1874777214716</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1644953289750935</v>
+        <v>0.1643709605408155</v>
       </c>
       <c r="C5">
-        <v>209.7695568009656</v>
+        <v>207.6044084485645</v>
       </c>
       <c r="D5">
-        <v>-13.13844319903444</v>
+        <v>-13.13959155143547</v>
       </c>
       <c r="E5">
-        <v>-36.408</v>
+        <v>-34.244</v>
       </c>
       <c r="F5">
-        <v>6.492</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="G5">
         <v>229.4</v>
@@ -1697,28 +1697,28 @@
         <v>104.883</v>
       </c>
       <c r="M5">
-        <v>0.3265476</v>
+        <v>0.4353968</v>
       </c>
       <c r="N5">
-        <v>104.5564524</v>
+        <v>104.4476032</v>
       </c>
       <c r="O5">
-        <v>10.45564524</v>
+        <v>10.44476032</v>
       </c>
       <c r="P5">
-        <v>94.10080716000002</v>
+        <v>94.00284288</v>
       </c>
       <c r="Q5">
-        <v>94.41780716000001</v>
+        <v>94.31984288</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1681827102836015</v>
+        <v>0.1693335005633495</v>
       </c>
       <c r="T5">
-        <v>0.7484774213169154</v>
+        <v>0.755515511412047</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>321.1874777214716</v>
+        <v>240.8906082911037</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1643709605408155</v>
+        <v>0.1642465921065376</v>
       </c>
       <c r="C6">
-        <v>207.6044084485645</v>
+        <v>205.4392598954048</v>
       </c>
       <c r="D6">
-        <v>-13.13959155143547</v>
+        <v>-13.14074010459521</v>
       </c>
       <c r="E6">
-        <v>-34.244</v>
+        <v>-32.08</v>
       </c>
       <c r="F6">
-        <v>8.656000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="G6">
         <v>229.4</v>
@@ -1779,28 +1779,28 @@
         <v>104.883</v>
       </c>
       <c r="M6">
-        <v>0.4353968</v>
+        <v>0.544246</v>
       </c>
       <c r="N6">
-        <v>104.4476032</v>
+        <v>104.338754</v>
       </c>
       <c r="O6">
-        <v>10.44476032</v>
+        <v>10.4338754</v>
       </c>
       <c r="P6">
-        <v>94.00284288</v>
+        <v>93.9048786</v>
       </c>
       <c r="Q6">
-        <v>94.31984288</v>
+        <v>94.2218786</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1693335005633495</v>
+        <v>0.1705085180068817</v>
       </c>
       <c r="T6">
-        <v>0.755515511412047</v>
+        <v>0.7627017718249706</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>240.8906082911037</v>
+        <v>192.7124866328829</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1642465921065376</v>
+        <v>0.1641222236722597</v>
       </c>
       <c r="C7">
-        <v>205.4392598954048</v>
+        <v>203.2741111414337</v>
       </c>
       <c r="D7">
-        <v>-13.14074010459521</v>
+        <v>-13.14188885856632</v>
       </c>
       <c r="E7">
-        <v>-32.08</v>
+        <v>-29.916</v>
       </c>
       <c r="F7">
-        <v>10.82</v>
+        <v>12.984</v>
       </c>
       <c r="G7">
         <v>229.4</v>
@@ -1861,28 +1861,28 @@
         <v>104.883</v>
       </c>
       <c r="M7">
-        <v>0.544246</v>
+        <v>0.6530952000000001</v>
       </c>
       <c r="N7">
-        <v>104.338754</v>
+        <v>104.2299048</v>
       </c>
       <c r="O7">
-        <v>10.4338754</v>
+        <v>10.42299048</v>
       </c>
       <c r="P7">
-        <v>93.9048786</v>
+        <v>93.80691432</v>
       </c>
       <c r="Q7">
-        <v>94.2218786</v>
+        <v>94.12391432</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1705085180068817</v>
+        <v>0.1717085358215528</v>
       </c>
       <c r="T7">
-        <v>0.7627017718249706</v>
+        <v>0.7700409313956161</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>192.7124866328829</v>
+        <v>160.5937388607358</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1641222236722597</v>
+        <v>0.1639978552379818</v>
       </c>
       <c r="C8">
-        <v>203.2741111414337</v>
+        <v>201.1089621865985</v>
       </c>
       <c r="D8">
-        <v>-13.14188885856632</v>
+        <v>-13.14303781340147</v>
       </c>
       <c r="E8">
-        <v>-29.916</v>
+        <v>-27.752</v>
       </c>
       <c r="F8">
-        <v>12.984</v>
+        <v>15.148</v>
       </c>
       <c r="G8">
         <v>229.4</v>
@@ -1943,28 +1943,28 @@
         <v>104.883</v>
       </c>
       <c r="M8">
-        <v>0.6530952</v>
+        <v>0.7619444</v>
       </c>
       <c r="N8">
-        <v>104.2299048</v>
+        <v>104.1210556</v>
       </c>
       <c r="O8">
-        <v>10.42299048</v>
+        <v>10.41210556</v>
       </c>
       <c r="P8">
-        <v>93.80691432</v>
+        <v>93.70895004</v>
       </c>
       <c r="Q8">
-        <v>94.12391432</v>
+        <v>94.02595004</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1717085358215528</v>
+        <v>0.1729343604709481</v>
       </c>
       <c r="T8">
-        <v>0.7700409313956161</v>
+        <v>0.7775379223548776</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>160.5937388607358</v>
+        <v>137.6517761663449</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1639978552379818</v>
+        <v>0.1638734868037038</v>
       </c>
       <c r="C9">
-        <v>201.1089621865985</v>
+        <v>198.9438130308467</v>
       </c>
       <c r="D9">
-        <v>-13.14303781340147</v>
+        <v>-13.14418696915335</v>
       </c>
       <c r="E9">
-        <v>-27.752</v>
+        <v>-25.588</v>
       </c>
       <c r="F9">
-        <v>15.148</v>
+        <v>17.312</v>
       </c>
       <c r="G9">
         <v>229.4</v>
@@ -2025,28 +2025,28 @@
         <v>104.883</v>
       </c>
       <c r="M9">
-        <v>0.7619444000000001</v>
+        <v>0.8707936000000001</v>
       </c>
       <c r="N9">
-        <v>104.1210556</v>
+        <v>104.0122064</v>
       </c>
       <c r="O9">
-        <v>10.41210556</v>
+        <v>10.40122064</v>
       </c>
       <c r="P9">
-        <v>93.70895004</v>
+        <v>93.61098576000001</v>
       </c>
       <c r="Q9">
-        <v>94.02595004</v>
+        <v>93.92798576</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1729343604709482</v>
+        <v>0.1741868334822868</v>
       </c>
       <c r="T9">
-        <v>0.7775379223548777</v>
+        <v>0.785197891378471</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>137.6517761663449</v>
+        <v>120.4453041455518</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1638734868037038</v>
+        <v>0.1637491183694259</v>
       </c>
       <c r="C10">
-        <v>198.9438130308467</v>
+        <v>196.7786636741254</v>
       </c>
       <c r="D10">
-        <v>-13.14418696915335</v>
+        <v>-13.14533632587465</v>
       </c>
       <c r="E10">
-        <v>-25.588</v>
+        <v>-23.424</v>
       </c>
       <c r="F10">
-        <v>17.312</v>
+        <v>19.476</v>
       </c>
       <c r="G10">
         <v>229.4</v>
@@ -2107,28 +2107,28 @@
         <v>104.883</v>
       </c>
       <c r="M10">
-        <v>0.8707936000000001</v>
+        <v>0.9796427999999999</v>
       </c>
       <c r="N10">
-        <v>104.0122064</v>
+        <v>103.9033572</v>
       </c>
       <c r="O10">
-        <v>10.40122064</v>
+        <v>10.39033572</v>
       </c>
       <c r="P10">
-        <v>93.61098576000001</v>
+        <v>93.51302148000002</v>
       </c>
       <c r="Q10">
-        <v>93.92798576</v>
+        <v>93.83002148000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1741868334822868</v>
+        <v>0.1754668333729955</v>
       </c>
       <c r="T10">
-        <v>0.785197891378471</v>
+        <v>0.7930262113696157</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>120.4453041455518</v>
+        <v>107.0624925738239</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1637491183694259</v>
+        <v>0.163624749935148</v>
       </c>
       <c r="C11">
-        <v>196.7786636741254</v>
+        <v>194.6135141163819</v>
       </c>
       <c r="D11">
-        <v>-13.14533632587465</v>
+        <v>-13.14648588361811</v>
       </c>
       <c r="E11">
-        <v>-23.424</v>
+        <v>-21.26</v>
       </c>
       <c r="F11">
-        <v>19.476</v>
+        <v>21.64</v>
       </c>
       <c r="G11">
         <v>229.4</v>
@@ -2189,28 +2189,28 @@
         <v>104.883</v>
       </c>
       <c r="M11">
-        <v>0.9796427999999999</v>
+        <v>1.088492</v>
       </c>
       <c r="N11">
-        <v>103.9033572</v>
+        <v>103.794508</v>
       </c>
       <c r="O11">
-        <v>10.39033572</v>
+        <v>10.3794508</v>
       </c>
       <c r="P11">
-        <v>93.51302148000002</v>
+        <v>93.41505720000001</v>
       </c>
       <c r="Q11">
-        <v>93.83002148000001</v>
+        <v>93.7320572</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1754668333729955</v>
+        <v>0.17677527770572</v>
       </c>
       <c r="T11">
-        <v>0.7930262113696157</v>
+        <v>0.8010284940272305</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>107.0624925738239</v>
+        <v>96.35624331644149</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.163624749935148</v>
+        <v>0.16350038150087</v>
       </c>
       <c r="C12">
-        <v>194.6135141163819</v>
+        <v>192.4483643575635</v>
       </c>
       <c r="D12">
-        <v>-13.14648588361811</v>
+        <v>-13.14763564243647</v>
       </c>
       <c r="E12">
-        <v>-21.26</v>
+        <v>-19.096</v>
       </c>
       <c r="F12">
-        <v>21.64</v>
+        <v>23.804</v>
       </c>
       <c r="G12">
         <v>229.4</v>
@@ -2271,28 +2271,28 @@
         <v>104.883</v>
       </c>
       <c r="M12">
-        <v>1.088492</v>
+        <v>1.1973412</v>
       </c>
       <c r="N12">
-        <v>103.794508</v>
+        <v>103.6856588</v>
       </c>
       <c r="O12">
-        <v>10.3794508</v>
+        <v>10.36856588</v>
       </c>
       <c r="P12">
-        <v>93.41505720000001</v>
+        <v>93.31709292000001</v>
       </c>
       <c r="Q12">
-        <v>93.7320572</v>
+        <v>93.63409292</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.17677527770572</v>
+        <v>0.1781131252818764</v>
       </c>
       <c r="T12">
-        <v>0.8010284940272305</v>
+        <v>0.8092106032614207</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>96.35624331644146</v>
+        <v>87.5965848331286</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.16350038150087</v>
+        <v>0.1633760130665921</v>
       </c>
       <c r="C13">
-        <v>192.4483643575635</v>
+        <v>190.2832143976175</v>
       </c>
       <c r="D13">
-        <v>-13.14763564243647</v>
+        <v>-13.14878560238249</v>
       </c>
       <c r="E13">
-        <v>-19.096</v>
+        <v>-16.932</v>
       </c>
       <c r="F13">
-        <v>23.804</v>
+        <v>25.968</v>
       </c>
       <c r="G13">
         <v>229.4</v>
@@ -2353,28 +2353,28 @@
         <v>104.883</v>
       </c>
       <c r="M13">
-        <v>1.1973412</v>
+        <v>1.3061904</v>
       </c>
       <c r="N13">
-        <v>103.6856588</v>
+        <v>103.5768096</v>
       </c>
       <c r="O13">
-        <v>10.36856588</v>
+        <v>10.35768096</v>
       </c>
       <c r="P13">
-        <v>93.31709292000001</v>
+        <v>93.21912864000001</v>
       </c>
       <c r="Q13">
-        <v>93.63409292</v>
+        <v>93.53612864</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1781131252818764</v>
+        <v>0.1794813784847638</v>
       </c>
       <c r="T13">
-        <v>0.8092106032614207</v>
+        <v>0.8175786695236609</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>87.5965848331286</v>
+        <v>80.29686943036789</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1633760130665921</v>
+        <v>0.1632516446323142</v>
       </c>
       <c r="C14">
-        <v>190.2832143976175</v>
+        <v>188.1180642364911</v>
       </c>
       <c r="D14">
-        <v>-13.14878560238249</v>
+        <v>-13.14993576350894</v>
       </c>
       <c r="E14">
-        <v>-16.932</v>
+        <v>-14.768</v>
       </c>
       <c r="F14">
-        <v>25.968</v>
+        <v>28.132</v>
       </c>
       <c r="G14">
         <v>229.4</v>
@@ -2435,28 +2435,28 @@
         <v>104.883</v>
       </c>
       <c r="M14">
-        <v>1.3061904</v>
+        <v>1.4150396</v>
       </c>
       <c r="N14">
-        <v>103.5768096</v>
+        <v>103.4679604</v>
       </c>
       <c r="O14">
-        <v>10.35768096</v>
+        <v>10.34679604</v>
       </c>
       <c r="P14">
-        <v>93.21912864000001</v>
+        <v>93.12116436000001</v>
       </c>
       <c r="Q14">
-        <v>93.53612864</v>
+        <v>93.43816436</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1794813784847638</v>
+        <v>0.1808810857842692</v>
       </c>
       <c r="T14">
-        <v>0.8175786695236609</v>
+        <v>0.8261391051252628</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>80.29686943036789</v>
+        <v>74.12018716649344</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1632516446323142</v>
+        <v>0.1631272761980363</v>
       </c>
       <c r="C15">
-        <v>188.1180642364911</v>
+        <v>185.9529138741314</v>
       </c>
       <c r="D15">
-        <v>-13.14993576350894</v>
+        <v>-13.15108612586864</v>
       </c>
       <c r="E15">
-        <v>-14.768</v>
+        <v>-12.604</v>
       </c>
       <c r="F15">
-        <v>28.132</v>
+        <v>30.296</v>
       </c>
       <c r="G15">
         <v>229.4</v>
@@ -2517,28 +2517,28 @@
         <v>104.883</v>
       </c>
       <c r="M15">
-        <v>1.4150396</v>
+        <v>1.5238888</v>
       </c>
       <c r="N15">
-        <v>103.4679604</v>
+        <v>103.3591112</v>
       </c>
       <c r="O15">
-        <v>10.34679604</v>
+        <v>10.33591112</v>
       </c>
       <c r="P15">
-        <v>93.12116436000001</v>
+        <v>93.02320008000001</v>
       </c>
       <c r="Q15">
-        <v>93.43816436</v>
+        <v>93.34020008</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1808810857842692</v>
+        <v>0.1823133444163212</v>
       </c>
       <c r="T15">
-        <v>0.8261391051252628</v>
+        <v>0.8348986206245763</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>74.12018716649344</v>
+        <v>68.82588808317247</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1631272761980363</v>
+        <v>0.1630029077637584</v>
       </c>
       <c r="C16">
-        <v>185.9529138741314</v>
+        <v>183.7877633104856</v>
       </c>
       <c r="D16">
-        <v>-13.15108612586864</v>
+        <v>-13.15223668951438</v>
       </c>
       <c r="E16">
-        <v>-12.604</v>
+        <v>-10.43999999999999</v>
       </c>
       <c r="F16">
-        <v>30.296</v>
+        <v>32.46000000000001</v>
       </c>
       <c r="G16">
         <v>229.4</v>
@@ -2599,28 +2599,28 @@
         <v>104.883</v>
       </c>
       <c r="M16">
-        <v>1.5238888</v>
+        <v>1.632738</v>
       </c>
       <c r="N16">
-        <v>103.3591112</v>
+        <v>103.250262</v>
       </c>
       <c r="O16">
-        <v>10.33591112</v>
+        <v>10.3250262</v>
       </c>
       <c r="P16">
-        <v>93.02320008000001</v>
+        <v>92.92523580000001</v>
       </c>
       <c r="Q16">
-        <v>93.34020008</v>
+        <v>93.2422358</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1823133444163212</v>
+        <v>0.1837793032514804</v>
       </c>
       <c r="T16">
-        <v>0.8348986206245763</v>
+        <v>0.8438642423709327</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>68.82588808317247</v>
+        <v>64.2374955442943</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1630029077637584</v>
+        <v>0.1628785393294804</v>
       </c>
       <c r="C17">
-        <v>183.7877633104856</v>
+        <v>181.622612545501</v>
       </c>
       <c r="D17">
-        <v>-13.15223668951438</v>
+        <v>-13.15338745449901</v>
       </c>
       <c r="E17">
-        <v>-10.44</v>
+        <v>-8.275999999999996</v>
       </c>
       <c r="F17">
-        <v>32.46</v>
+        <v>34.624</v>
       </c>
       <c r="G17">
         <v>229.4</v>
@@ -2681,28 +2681,28 @@
         <v>104.883</v>
       </c>
       <c r="M17">
-        <v>1.632738</v>
+        <v>1.7415872</v>
       </c>
       <c r="N17">
-        <v>103.250262</v>
+        <v>103.1414128</v>
       </c>
       <c r="O17">
-        <v>10.3250262</v>
+        <v>10.31414128</v>
       </c>
       <c r="P17">
-        <v>92.92523580000001</v>
+        <v>92.82727152000001</v>
       </c>
       <c r="Q17">
-        <v>93.2422358</v>
+        <v>93.14427152</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1837793032514804</v>
+        <v>0.1852801658684291</v>
       </c>
       <c r="T17">
-        <v>0.8438642423709327</v>
+        <v>0.853043331301726</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>64.23749554429432</v>
+        <v>60.22265207277592</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1628785393294804</v>
+        <v>0.1627541708952025</v>
       </c>
       <c r="C18">
-        <v>181.622612545501</v>
+        <v>179.4574615791246</v>
       </c>
       <c r="D18">
-        <v>-13.15338745449901</v>
+        <v>-13.15453842087539</v>
       </c>
       <c r="E18">
-        <v>-8.275999999999996</v>
+        <v>-6.111999999999995</v>
       </c>
       <c r="F18">
-        <v>34.624</v>
+        <v>36.788</v>
       </c>
       <c r="G18">
         <v>229.4</v>
@@ -2763,28 +2763,28 @@
         <v>104.883</v>
       </c>
       <c r="M18">
-        <v>1.7415872</v>
+        <v>1.8504364</v>
       </c>
       <c r="N18">
-        <v>103.1414128</v>
+        <v>103.0325636</v>
       </c>
       <c r="O18">
-        <v>10.31414128</v>
+        <v>10.30325636</v>
       </c>
       <c r="P18">
-        <v>92.82727152000001</v>
+        <v>92.72930724</v>
       </c>
       <c r="Q18">
-        <v>93.14427152</v>
+        <v>93.04630723999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1852801658684291</v>
+        <v>0.1868171938496416</v>
       </c>
       <c r="T18">
-        <v>0.853043331301726</v>
+        <v>0.8624436030983216</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>60.22265207277592</v>
+        <v>56.6801431273185</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1627541708952025</v>
+        <v>0.1626298024609246</v>
       </c>
       <c r="C19">
-        <v>179.4574615791246</v>
+        <v>177.2923104113036</v>
       </c>
       <c r="D19">
-        <v>-13.15453842087539</v>
+        <v>-13.15568958869638</v>
       </c>
       <c r="E19">
-        <v>-6.111999999999995</v>
+        <v>-3.947999999999993</v>
       </c>
       <c r="F19">
-        <v>36.788</v>
+        <v>38.95200000000001</v>
       </c>
       <c r="G19">
         <v>229.4</v>
@@ -2845,28 +2845,28 @@
         <v>104.883</v>
       </c>
       <c r="M19">
-        <v>1.8504364</v>
+        <v>1.9592856</v>
       </c>
       <c r="N19">
-        <v>103.0325636</v>
+        <v>102.9237144</v>
       </c>
       <c r="O19">
-        <v>10.30325636</v>
+        <v>10.29237144</v>
       </c>
       <c r="P19">
-        <v>92.72930724</v>
+        <v>92.63134296000001</v>
       </c>
       <c r="Q19">
-        <v>93.04630723999999</v>
+        <v>92.94834296000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1868171938496416</v>
+        <v>0.1883917103182007</v>
       </c>
       <c r="T19">
-        <v>0.8624436030983216</v>
+        <v>0.8720731498167853</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>56.6801431273185</v>
+        <v>53.53124628691192</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1626298024609246</v>
+        <v>0.1625054340266466</v>
       </c>
       <c r="C20">
-        <v>177.2923104113036</v>
+        <v>175.1271590419851</v>
       </c>
       <c r="D20">
-        <v>-13.15568958869638</v>
+        <v>-13.15684095801488</v>
       </c>
       <c r="E20">
-        <v>-3.948</v>
+        <v>-1.783999999999999</v>
       </c>
       <c r="F20">
-        <v>38.952</v>
+        <v>41.116</v>
       </c>
       <c r="G20">
         <v>229.4</v>
@@ -2927,28 +2927,28 @@
         <v>104.883</v>
       </c>
       <c r="M20">
-        <v>1.9592856</v>
+        <v>2.0681348</v>
       </c>
       <c r="N20">
-        <v>102.9237144</v>
+        <v>102.8148652</v>
       </c>
       <c r="O20">
-        <v>10.29237144</v>
+        <v>10.28148652</v>
       </c>
       <c r="P20">
-        <v>92.63134296000001</v>
+        <v>92.53337868000001</v>
       </c>
       <c r="Q20">
-        <v>92.94834296000001</v>
+        <v>92.85037868000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1883917103182007</v>
+        <v>0.1900051037366008</v>
       </c>
       <c r="T20">
-        <v>0.8720731498167853</v>
+        <v>0.88194046312089</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>53.53124628691193</v>
+        <v>50.71381227181131</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1625054340266466</v>
+        <v>0.1623810655923688</v>
       </c>
       <c r="C21">
-        <v>175.1271590419851</v>
+        <v>172.9620074711162</v>
       </c>
       <c r="D21">
-        <v>-13.15684095801488</v>
+        <v>-13.15799252888378</v>
       </c>
       <c r="E21">
-        <v>-1.783999999999999</v>
+        <v>0.3800000000000026</v>
       </c>
       <c r="F21">
-        <v>41.116</v>
+        <v>43.28</v>
       </c>
       <c r="G21">
         <v>229.4</v>
@@ -3009,28 +3009,28 @@
         <v>104.883</v>
       </c>
       <c r="M21">
-        <v>2.0681348</v>
+        <v>2.176984</v>
       </c>
       <c r="N21">
-        <v>102.8148652</v>
+        <v>102.706016</v>
       </c>
       <c r="O21">
-        <v>10.28148652</v>
+        <v>10.2706016</v>
       </c>
       <c r="P21">
-        <v>92.53337868000001</v>
+        <v>92.4354144</v>
       </c>
       <c r="Q21">
-        <v>92.85037868000001</v>
+        <v>92.75241439999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1900051037366008</v>
+        <v>0.1916588319904609</v>
       </c>
       <c r="T21">
-        <v>0.88194046312089</v>
+        <v>0.8920544592575976</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>50.71381227181131</v>
+        <v>48.17812165822073</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1623810655923688</v>
+        <v>0.1622566971580908</v>
       </c>
       <c r="C22">
-        <v>172.9620074711162</v>
+        <v>170.796855698644</v>
       </c>
       <c r="D22">
-        <v>-13.15799252888378</v>
+        <v>-13.15914430135603</v>
       </c>
       <c r="E22">
-        <v>0.3800000000000026</v>
+        <v>2.544000000000004</v>
       </c>
       <c r="F22">
-        <v>43.28</v>
+        <v>45.444</v>
       </c>
       <c r="G22">
         <v>229.4</v>
@@ -3091,28 +3091,28 @@
         <v>104.883</v>
       </c>
       <c r="M22">
-        <v>2.176984</v>
+        <v>2.2858332</v>
       </c>
       <c r="N22">
-        <v>102.706016</v>
+        <v>102.5971668</v>
       </c>
       <c r="O22">
-        <v>10.2706016</v>
+        <v>10.25971668</v>
       </c>
       <c r="P22">
-        <v>92.4354144</v>
+        <v>92.33745012000001</v>
       </c>
       <c r="Q22">
-        <v>92.75241439999999</v>
+        <v>92.65445012000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1916588319904609</v>
+        <v>0.1933544267823934</v>
       </c>
       <c r="T22">
-        <v>0.8920544592575976</v>
+        <v>0.9024245059294115</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>48.17812165822073</v>
+        <v>45.88392538878166</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1622566971580908</v>
+        <v>0.1621323287238129</v>
       </c>
       <c r="C23">
-        <v>170.796855698644</v>
+        <v>168.6317037245154</v>
       </c>
       <c r="D23">
-        <v>-13.15914430135603</v>
+        <v>-13.16029627548456</v>
       </c>
       <c r="E23">
-        <v>2.544000000000004</v>
+        <v>4.708000000000006</v>
       </c>
       <c r="F23">
-        <v>45.444</v>
+        <v>47.608</v>
       </c>
       <c r="G23">
         <v>229.4</v>
@@ -3173,28 +3173,28 @@
         <v>104.883</v>
       </c>
       <c r="M23">
-        <v>2.2858332</v>
+        <v>2.3946824</v>
       </c>
       <c r="N23">
-        <v>102.5971668</v>
+        <v>102.4883176</v>
       </c>
       <c r="O23">
-        <v>10.25971668</v>
+        <v>10.24883176</v>
       </c>
       <c r="P23">
-        <v>92.33745012000001</v>
+        <v>92.23948584000001</v>
       </c>
       <c r="Q23">
-        <v>92.65445012000001</v>
+        <v>92.55648584000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1933544267823934</v>
+        <v>0.1950934983638626</v>
       </c>
       <c r="T23">
-        <v>0.9024245059294115</v>
+        <v>0.9130604512338362</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>45.88392538878166</v>
+        <v>43.7982924165643</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1621323287238129</v>
+        <v>0.1620079602895349</v>
       </c>
       <c r="C24">
-        <v>168.6317037245154</v>
+        <v>166.4665515486777</v>
       </c>
       <c r="D24">
-        <v>-13.16029627548456</v>
+        <v>-13.16144845132235</v>
       </c>
       <c r="E24">
-        <v>4.708000000000006</v>
+        <v>6.872000000000007</v>
       </c>
       <c r="F24">
-        <v>47.608</v>
+        <v>49.77200000000001</v>
       </c>
       <c r="G24">
         <v>229.4</v>
@@ -3255,28 +3255,28 @@
         <v>104.883</v>
       </c>
       <c r="M24">
-        <v>2.3946824</v>
+        <v>2.5035316</v>
       </c>
       <c r="N24">
-        <v>102.4883176</v>
+        <v>102.3794684</v>
       </c>
       <c r="O24">
-        <v>10.24883176</v>
+        <v>10.23794684</v>
       </c>
       <c r="P24">
-        <v>92.23948584000001</v>
+        <v>92.14152156</v>
       </c>
       <c r="Q24">
-        <v>92.55648584000001</v>
+        <v>92.45852155999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1950934983638626</v>
+        <v>0.1968777406357596</v>
       </c>
       <c r="T24">
-        <v>0.9130604512338362</v>
+        <v>0.9239726548578562</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>43.7982924165643</v>
+        <v>41.89401883323542</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1620079602895349</v>
+        <v>0.161883591855257</v>
       </c>
       <c r="C25">
-        <v>166.4665515486777</v>
+        <v>164.3013991710776</v>
       </c>
       <c r="D25">
-        <v>-13.16144845132235</v>
+        <v>-13.16260082892237</v>
       </c>
       <c r="E25">
-        <v>6.872000000000007</v>
+        <v>9.036000000000008</v>
       </c>
       <c r="F25">
-        <v>49.77200000000001</v>
+        <v>51.93600000000001</v>
       </c>
       <c r="G25">
         <v>229.4</v>
@@ -3337,28 +3337,28 @@
         <v>104.883</v>
       </c>
       <c r="M25">
-        <v>2.5035316</v>
+        <v>2.6123808</v>
       </c>
       <c r="N25">
-        <v>102.3794684</v>
+        <v>102.2706192</v>
       </c>
       <c r="O25">
-        <v>10.23794684</v>
+        <v>10.22706192</v>
       </c>
       <c r="P25">
-        <v>92.14152156</v>
+        <v>92.04355728000002</v>
       </c>
       <c r="Q25">
-        <v>92.45852155999999</v>
+        <v>92.36055728000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1968777406357596</v>
+        <v>0.198708936651654</v>
       </c>
       <c r="T25">
-        <v>0.9239726548578562</v>
+        <v>0.9351720217351399</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>41.89401883323542</v>
+        <v>40.14843471518394</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.161883591855257</v>
+        <v>0.1617592234209791</v>
       </c>
       <c r="C26">
-        <v>164.3013991710776</v>
+        <v>162.1362465916624</v>
       </c>
       <c r="D26">
-        <v>-13.16260082892237</v>
+        <v>-13.16375340833763</v>
       </c>
       <c r="E26">
-        <v>9.036000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="F26">
-        <v>51.936</v>
+        <v>54.1</v>
       </c>
       <c r="G26">
         <v>229.4</v>
@@ -3419,28 +3419,28 @@
         <v>104.883</v>
       </c>
       <c r="M26">
-        <v>2.6123808</v>
+        <v>2.72123</v>
       </c>
       <c r="N26">
-        <v>102.2706192</v>
+        <v>102.16177</v>
       </c>
       <c r="O26">
-        <v>10.22706192</v>
+        <v>10.216177</v>
       </c>
       <c r="P26">
-        <v>92.04355728000002</v>
+        <v>91.945593</v>
       </c>
       <c r="Q26">
-        <v>92.36055728000001</v>
+        <v>92.262593</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.198708936651654</v>
+        <v>0.2005889645613054</v>
       </c>
       <c r="T26">
-        <v>0.9351720217351399</v>
+        <v>0.9466700383958179</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>40.14843471518395</v>
+        <v>38.54249732657659</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1617592234209791</v>
+        <v>0.1616348549867012</v>
       </c>
       <c r="C27">
-        <v>162.1362465916624</v>
+        <v>159.9710938103788</v>
       </c>
       <c r="D27">
-        <v>-13.16375340833763</v>
+        <v>-13.16490618962115</v>
       </c>
       <c r="E27">
-        <v>11.2</v>
+        <v>13.364</v>
       </c>
       <c r="F27">
-        <v>54.1</v>
+        <v>56.264</v>
       </c>
       <c r="G27">
         <v>229.4</v>
@@ -3501,28 +3501,28 @@
         <v>104.883</v>
       </c>
       <c r="M27">
-        <v>2.72123</v>
+        <v>2.8300792</v>
       </c>
       <c r="N27">
-        <v>102.16177</v>
+        <v>102.0529208</v>
       </c>
       <c r="O27">
-        <v>10.216177</v>
+        <v>10.20529208</v>
       </c>
       <c r="P27">
-        <v>91.945593</v>
+        <v>91.84762872</v>
       </c>
       <c r="Q27">
-        <v>92.262593</v>
+        <v>92.16462872</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2005889645613054</v>
+        <v>0.2025198040360827</v>
       </c>
       <c r="T27">
-        <v>0.9466700383958179</v>
+        <v>0.9584788122635413</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>38.54249732657659</v>
+        <v>37.06009358324672</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1616348549867012</v>
+        <v>0.1615104865524233</v>
       </c>
       <c r="C28">
-        <v>159.9710938103788</v>
+        <v>157.8059408271741</v>
       </c>
       <c r="D28">
-        <v>-13.16490618962115</v>
+        <v>-13.16605917282596</v>
       </c>
       <c r="E28">
-        <v>13.364</v>
+        <v>15.52800000000001</v>
       </c>
       <c r="F28">
-        <v>56.264</v>
+        <v>58.428</v>
       </c>
       <c r="G28">
         <v>229.4</v>
@@ -3583,28 +3583,28 @@
         <v>104.883</v>
       </c>
       <c r="M28">
-        <v>2.8300792</v>
+        <v>2.9389284</v>
       </c>
       <c r="N28">
-        <v>102.0529208</v>
+        <v>101.9440716</v>
       </c>
       <c r="O28">
-        <v>10.20529208</v>
+        <v>10.19440716</v>
       </c>
       <c r="P28">
-        <v>91.84762872</v>
+        <v>91.74966444000002</v>
       </c>
       <c r="Q28">
-        <v>92.16462872</v>
+        <v>92.06666444000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2025198040360827</v>
+        <v>0.2045035432224976</v>
       </c>
       <c r="T28">
-        <v>0.9584788122635413</v>
+        <v>0.9706111141824351</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>37.06009358324672</v>
+        <v>35.68749752460796</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1615104865524233</v>
+        <v>0.1613861181181453</v>
       </c>
       <c r="C29">
-        <v>157.8059408271741</v>
+        <v>155.6407876419949</v>
       </c>
       <c r="D29">
-        <v>-13.16605917282596</v>
+        <v>-13.16721235800512</v>
       </c>
       <c r="E29">
-        <v>15.52800000000001</v>
+        <v>17.69200000000001</v>
       </c>
       <c r="F29">
-        <v>58.428</v>
+        <v>60.59200000000001</v>
       </c>
       <c r="G29">
         <v>229.4</v>
@@ -3665,28 +3665,28 @@
         <v>104.883</v>
       </c>
       <c r="M29">
-        <v>2.9389284</v>
+        <v>3.0477776</v>
       </c>
       <c r="N29">
-        <v>101.9440716</v>
+        <v>101.8352224</v>
       </c>
       <c r="O29">
-        <v>10.19440716</v>
+        <v>10.18352224</v>
       </c>
       <c r="P29">
-        <v>91.74966444000002</v>
+        <v>91.65170016</v>
       </c>
       <c r="Q29">
-        <v>92.06666444000001</v>
+        <v>91.96870016</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2045035432224976</v>
+        <v>0.2065423862752018</v>
       </c>
       <c r="T29">
-        <v>0.9706111141824351</v>
+        <v>0.9830804244879647</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>35.68749752460796</v>
+        <v>34.41294404158624</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1613861181181453</v>
+        <v>0.1612617496838674</v>
       </c>
       <c r="C30">
-        <v>155.6407876419949</v>
+        <v>153.4756342547883</v>
       </c>
       <c r="D30">
-        <v>-13.16721235800512</v>
+        <v>-13.16836574521171</v>
       </c>
       <c r="E30">
-        <v>17.69200000000001</v>
+        <v>19.85600000000001</v>
       </c>
       <c r="F30">
-        <v>60.59200000000001</v>
+        <v>62.75600000000001</v>
       </c>
       <c r="G30">
         <v>229.4</v>
@@ -3747,28 +3747,28 @@
         <v>104.883</v>
       </c>
       <c r="M30">
-        <v>3.0477776</v>
+        <v>3.1566268</v>
       </c>
       <c r="N30">
-        <v>101.8352224</v>
+        <v>101.7263732</v>
       </c>
       <c r="O30">
-        <v>10.18352224</v>
+        <v>10.17263732</v>
       </c>
       <c r="P30">
-        <v>91.65170016</v>
+        <v>91.55373588</v>
       </c>
       <c r="Q30">
-        <v>91.96870016</v>
+        <v>91.87073588</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2065423862752018</v>
+        <v>0.2086386615265738</v>
       </c>
       <c r="T30">
-        <v>0.9830804244879647</v>
+        <v>0.9959009829711151</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>34.41294404158624</v>
+        <v>33.22629079877292</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1612617496838674</v>
+        <v>0.1611373812495894</v>
       </c>
       <c r="C31">
-        <v>153.4756342547883</v>
+        <v>151.3104806655012</v>
       </c>
       <c r="D31">
-        <v>-13.16836574521171</v>
+        <v>-13.16951933449883</v>
       </c>
       <c r="E31">
-        <v>19.856</v>
+        <v>22.02</v>
       </c>
       <c r="F31">
-        <v>62.756</v>
+        <v>64.92</v>
       </c>
       <c r="G31">
         <v>229.4</v>
@@ -3829,28 +3829,28 @@
         <v>104.883</v>
       </c>
       <c r="M31">
-        <v>3.1566268</v>
+        <v>3.265476</v>
       </c>
       <c r="N31">
-        <v>101.7263732</v>
+        <v>101.617524</v>
       </c>
       <c r="O31">
-        <v>10.17263732</v>
+        <v>10.1617524</v>
       </c>
       <c r="P31">
-        <v>91.55373588</v>
+        <v>91.45577160000001</v>
       </c>
       <c r="Q31">
-        <v>91.87073588</v>
+        <v>91.7727716</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2086386615265738</v>
+        <v>0.2107948303565563</v>
       </c>
       <c r="T31">
-        <v>0.995900982971115</v>
+        <v>1.009087843125212</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>33.22629079877292</v>
+        <v>32.11874777214716</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1611373812495894</v>
+        <v>0.1610130128153115</v>
       </c>
       <c r="C32">
-        <v>151.3104806655012</v>
+        <v>149.1453268740804</v>
       </c>
       <c r="D32">
-        <v>-13.16951933449883</v>
+        <v>-13.17067312591959</v>
       </c>
       <c r="E32">
-        <v>22.02</v>
+        <v>24.184</v>
       </c>
       <c r="F32">
-        <v>64.92</v>
+        <v>67.084</v>
       </c>
       <c r="G32">
         <v>229.4</v>
@@ -3911,28 +3911,28 @@
         <v>104.883</v>
       </c>
       <c r="M32">
-        <v>3.265476</v>
+        <v>3.3743252</v>
       </c>
       <c r="N32">
-        <v>101.617524</v>
+        <v>101.5086748</v>
       </c>
       <c r="O32">
-        <v>10.1617524</v>
+        <v>10.15086748</v>
       </c>
       <c r="P32">
-        <v>91.45577160000001</v>
+        <v>91.35780732000001</v>
       </c>
       <c r="Q32">
-        <v>91.7727716</v>
+        <v>91.67480732</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2107948303565563</v>
+        <v>0.2130134968337848</v>
       </c>
       <c r="T32">
-        <v>1.009087843125212</v>
+        <v>1.022656931109863</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>32.11874777214716</v>
+        <v>31.08265913433596</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1610130128153115</v>
+        <v>0.1608886443810336</v>
       </c>
       <c r="C33">
-        <v>149.1453268740804</v>
+        <v>146.9801728804729</v>
       </c>
       <c r="D33">
-        <v>-13.17067312591959</v>
+        <v>-13.17182711952711</v>
       </c>
       <c r="E33">
-        <v>24.184</v>
+        <v>26.34800000000001</v>
       </c>
       <c r="F33">
-        <v>67.084</v>
+        <v>69.248</v>
       </c>
       <c r="G33">
         <v>229.4</v>
@@ -3993,28 +3993,28 @@
         <v>104.883</v>
       </c>
       <c r="M33">
-        <v>3.3743252</v>
+        <v>3.4831744</v>
       </c>
       <c r="N33">
-        <v>101.5086748</v>
+        <v>101.3998256</v>
       </c>
       <c r="O33">
-        <v>10.15086748</v>
+        <v>10.13998256</v>
       </c>
       <c r="P33">
-        <v>91.35780732000001</v>
+        <v>91.25984304000001</v>
       </c>
       <c r="Q33">
-        <v>91.67480732</v>
+        <v>91.57684304</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2130134968337848</v>
+        <v>0.2152974182074023</v>
       </c>
       <c r="T33">
-        <v>1.022656931109863</v>
+        <v>1.036625109917592</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>31.08265913433596</v>
+        <v>30.11132603638796</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1608886443810336</v>
+        <v>0.1607642759467557</v>
       </c>
       <c r="C34">
-        <v>146.9801728804729</v>
+        <v>144.8150186846254</v>
       </c>
       <c r="D34">
-        <v>-13.17182711952711</v>
+        <v>-13.17298131537455</v>
       </c>
       <c r="E34">
-        <v>26.34800000000001</v>
+        <v>28.51200000000001</v>
       </c>
       <c r="F34">
-        <v>69.248</v>
+        <v>71.41200000000001</v>
       </c>
       <c r="G34">
         <v>229.4</v>
@@ -4075,28 +4075,28 @@
         <v>104.883</v>
       </c>
       <c r="M34">
-        <v>3.4831744</v>
+        <v>3.5920236</v>
       </c>
       <c r="N34">
-        <v>101.3998256</v>
+        <v>101.2909764</v>
       </c>
       <c r="O34">
-        <v>10.13998256</v>
+        <v>10.12909764</v>
       </c>
       <c r="P34">
-        <v>91.25984304000001</v>
+        <v>91.16187876000001</v>
       </c>
       <c r="Q34">
-        <v>91.57684304</v>
+        <v>91.47887876</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2152974182074023</v>
+        <v>0.2176495163384413</v>
       </c>
       <c r="T34">
-        <v>1.036625109917592</v>
+        <v>1.051010249286746</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>30.11132603638796</v>
+        <v>29.19886161104287</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1607642759467557</v>
+        <v>0.1606399075124777</v>
       </c>
       <c r="C35">
-        <v>144.8150186846254</v>
+        <v>142.6498642864849</v>
       </c>
       <c r="D35">
-        <v>-13.17298131537455</v>
+        <v>-13.17413571351509</v>
       </c>
       <c r="E35">
-        <v>28.51200000000001</v>
+        <v>30.67600000000001</v>
       </c>
       <c r="F35">
-        <v>71.41200000000001</v>
+        <v>73.57600000000001</v>
       </c>
       <c r="G35">
         <v>229.4</v>
@@ -4157,28 +4157,28 @@
         <v>104.883</v>
       </c>
       <c r="M35">
-        <v>3.5920236</v>
+        <v>3.7008728</v>
       </c>
       <c r="N35">
-        <v>101.2909764</v>
+        <v>101.1821272</v>
       </c>
       <c r="O35">
-        <v>10.12909764</v>
+        <v>10.11821272</v>
       </c>
       <c r="P35">
-        <v>91.16187876000001</v>
+        <v>91.06391448000001</v>
       </c>
       <c r="Q35">
-        <v>91.47887876</v>
+        <v>91.38091448</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2176495163384413</v>
+        <v>0.2200728901704208</v>
       </c>
       <c r="T35">
-        <v>1.051010249286746</v>
+        <v>1.065831301970117</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>29.19886161104287</v>
+        <v>28.34007156365925</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1606399075124777</v>
+        <v>0.1605155390781998</v>
       </c>
       <c r="C36">
-        <v>142.6498642864849</v>
+        <v>140.4847096859981</v>
       </c>
       <c r="D36">
-        <v>-13.17413571351509</v>
+        <v>-13.1752903140019</v>
       </c>
       <c r="E36">
-        <v>30.67600000000001</v>
+        <v>32.84000000000001</v>
       </c>
       <c r="F36">
-        <v>73.57600000000001</v>
+        <v>75.74000000000001</v>
       </c>
       <c r="G36">
         <v>229.4</v>
@@ -4239,28 +4239,28 @@
         <v>104.883</v>
       </c>
       <c r="M36">
-        <v>3.7008728</v>
+        <v>3.809722</v>
       </c>
       <c r="N36">
-        <v>101.1821272</v>
+        <v>101.073278</v>
       </c>
       <c r="O36">
-        <v>10.11821272</v>
+        <v>10.1073278</v>
       </c>
       <c r="P36">
-        <v>91.06391448000001</v>
+        <v>90.96595020000001</v>
       </c>
       <c r="Q36">
-        <v>91.38091448</v>
+        <v>91.2829502</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2200728901704208</v>
+        <v>0.2225708293510766</v>
       </c>
       <c r="T36">
-        <v>1.065831301970117</v>
+        <v>1.081108387043745</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>28.34007156365925</v>
+        <v>27.53035523326899</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1605155390781998</v>
+        <v>0.1603911706439219</v>
       </c>
       <c r="C37">
-        <v>140.4847096859981</v>
+        <v>138.3195548831118</v>
       </c>
       <c r="D37">
-        <v>-13.1752903140019</v>
+        <v>-13.17644511688819</v>
       </c>
       <c r="E37">
-        <v>32.84000000000001</v>
+        <v>35.00400000000001</v>
       </c>
       <c r="F37">
-        <v>75.74000000000001</v>
+        <v>77.90400000000001</v>
       </c>
       <c r="G37">
         <v>229.4</v>
@@ -4321,28 +4321,28 @@
         <v>104.883</v>
       </c>
       <c r="M37">
-        <v>3.809722</v>
+        <v>3.9185712</v>
       </c>
       <c r="N37">
-        <v>101.073278</v>
+        <v>100.9644288</v>
       </c>
       <c r="O37">
-        <v>10.1073278</v>
+        <v>10.09644288</v>
       </c>
       <c r="P37">
-        <v>90.96595020000001</v>
+        <v>90.86798592000001</v>
       </c>
       <c r="Q37">
-        <v>91.2829502</v>
+        <v>91.18498592</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2225708293510766</v>
+        <v>0.2251468291311279</v>
       </c>
       <c r="T37">
-        <v>1.081108387043745</v>
+        <v>1.096862881025924</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>27.53035523326899</v>
+        <v>26.76562314345596</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1603911706439219</v>
+        <v>0.160266802209644</v>
       </c>
       <c r="C38">
-        <v>138.3195548831118</v>
+        <v>136.1543998777728</v>
       </c>
       <c r="D38">
-        <v>-13.17644511688819</v>
+        <v>-13.17760012222719</v>
       </c>
       <c r="E38">
-        <v>35.004</v>
+        <v>37.168</v>
       </c>
       <c r="F38">
-        <v>77.904</v>
+        <v>80.068</v>
       </c>
       <c r="G38">
         <v>229.4</v>
@@ -4403,28 +4403,28 @@
         <v>104.883</v>
       </c>
       <c r="M38">
-        <v>3.9185712</v>
+        <v>4.0274204</v>
       </c>
       <c r="N38">
-        <v>100.9644288</v>
+        <v>100.8555796</v>
       </c>
       <c r="O38">
-        <v>10.09644288</v>
+        <v>10.08555796</v>
       </c>
       <c r="P38">
-        <v>90.86798592000001</v>
+        <v>90.77002164000001</v>
       </c>
       <c r="Q38">
-        <v>91.18498592</v>
+        <v>91.08702164</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2251468291311279</v>
+        <v>0.2278046066819745</v>
       </c>
       <c r="T38">
-        <v>1.096862881025924</v>
+        <v>1.113117517674203</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>26.76562314345597</v>
+        <v>26.04222792336256</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.160266802209644</v>
+        <v>0.160142433775366</v>
       </c>
       <c r="C39">
-        <v>136.1543998777728</v>
+        <v>133.9892446699279</v>
       </c>
       <c r="D39">
-        <v>-13.17760012222719</v>
+        <v>-13.17875533007214</v>
       </c>
       <c r="E39">
-        <v>37.168</v>
+        <v>39.332</v>
       </c>
       <c r="F39">
-        <v>80.068</v>
+        <v>82.232</v>
       </c>
       <c r="G39">
         <v>229.4</v>
@@ -4485,28 +4485,28 @@
         <v>104.883</v>
       </c>
       <c r="M39">
-        <v>4.0274204</v>
+        <v>4.136269599999999</v>
       </c>
       <c r="N39">
-        <v>100.8555796</v>
+        <v>100.7467304</v>
       </c>
       <c r="O39">
-        <v>10.08555796</v>
+        <v>10.07467304</v>
       </c>
       <c r="P39">
-        <v>90.77002164000001</v>
+        <v>90.67205736</v>
       </c>
       <c r="Q39">
-        <v>91.08702164</v>
+        <v>90.98905735999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2278046066819745</v>
+        <v>0.2305481189925258</v>
       </c>
       <c r="T39">
-        <v>1.113117517674203</v>
+        <v>1.12989649744017</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>26.04222792336256</v>
+        <v>25.35690613590565</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.160142433775366</v>
+        <v>0.1600180653410881</v>
       </c>
       <c r="C40">
-        <v>133.9892446699279</v>
+        <v>131.8240892595237</v>
       </c>
       <c r="D40">
-        <v>-13.17875533007214</v>
+        <v>-13.17991074047631</v>
       </c>
       <c r="E40">
-        <v>39.332</v>
+        <v>41.496</v>
       </c>
       <c r="F40">
-        <v>82.232</v>
+        <v>84.396</v>
       </c>
       <c r="G40">
         <v>229.4</v>
@@ -4567,28 +4567,28 @@
         <v>104.883</v>
       </c>
       <c r="M40">
-        <v>4.136269599999999</v>
+        <v>4.2451188</v>
       </c>
       <c r="N40">
-        <v>100.7467304</v>
+        <v>100.6378812</v>
       </c>
       <c r="O40">
-        <v>10.07467304</v>
+        <v>10.06378812</v>
       </c>
       <c r="P40">
-        <v>90.67205736</v>
+        <v>90.57409308000001</v>
       </c>
       <c r="Q40">
-        <v>90.98905735999999</v>
+        <v>90.89109308</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2305481189925258</v>
+        <v>0.2333815825263739</v>
       </c>
       <c r="T40">
-        <v>1.12989649744017</v>
+        <v>1.147225607690266</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>25.35690613590565</v>
+        <v>24.70672905549781</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1600180653410881</v>
+        <v>0.1598936969068102</v>
       </c>
       <c r="C41">
-        <v>131.8240892595237</v>
+        <v>129.658933646507</v>
       </c>
       <c r="D41">
-        <v>-13.17991074047631</v>
+        <v>-13.18106635349297</v>
       </c>
       <c r="E41">
-        <v>41.496</v>
+        <v>43.66</v>
       </c>
       <c r="F41">
-        <v>84.396</v>
+        <v>86.56</v>
       </c>
       <c r="G41">
         <v>229.4</v>
@@ -4649,28 +4649,28 @@
         <v>104.883</v>
       </c>
       <c r="M41">
-        <v>4.2451188</v>
+        <v>4.353968</v>
       </c>
       <c r="N41">
-        <v>100.6378812</v>
+        <v>100.529032</v>
       </c>
       <c r="O41">
-        <v>10.06378812</v>
+        <v>10.0529032</v>
       </c>
       <c r="P41">
-        <v>90.57409308000001</v>
+        <v>90.47612880000001</v>
       </c>
       <c r="Q41">
-        <v>90.89109308</v>
+        <v>90.79312880000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2333815825263739</v>
+        <v>0.2363094948446836</v>
       </c>
       <c r="T41">
-        <v>1.147225607690266</v>
+        <v>1.165132354948699</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>24.70672905549781</v>
+        <v>24.08906082911037</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1598936969068102</v>
+        <v>0.1597693284725322</v>
       </c>
       <c r="C42">
-        <v>129.658933646507</v>
+        <v>127.4937778308246</v>
       </c>
       <c r="D42">
-        <v>-13.18106635349297</v>
+        <v>-13.18222216917543</v>
       </c>
       <c r="E42">
-        <v>43.66</v>
+        <v>45.82400000000001</v>
       </c>
       <c r="F42">
-        <v>86.56</v>
+        <v>88.724</v>
       </c>
       <c r="G42">
         <v>229.4</v>
@@ -4731,28 +4731,28 @@
         <v>104.883</v>
       </c>
       <c r="M42">
-        <v>4.353968</v>
+        <v>4.4628172</v>
       </c>
       <c r="N42">
-        <v>100.529032</v>
+        <v>100.4201828</v>
       </c>
       <c r="O42">
-        <v>10.0529032</v>
+        <v>10.04201828</v>
       </c>
       <c r="P42">
-        <v>90.47612880000001</v>
+        <v>90.37816452000001</v>
       </c>
       <c r="Q42">
-        <v>90.79312880000001</v>
+        <v>90.69516452000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2363094948446836</v>
+        <v>0.2393366584280208</v>
       </c>
       <c r="T42">
-        <v>1.165132354948699</v>
+        <v>1.183646110588774</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>24.08906082911037</v>
+        <v>23.50152276010768</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1597693284725322</v>
+        <v>0.1596449600382543</v>
       </c>
       <c r="C43">
-        <v>127.4937778308246</v>
+        <v>125.328621812423</v>
       </c>
       <c r="D43">
-        <v>-13.18222216917543</v>
+        <v>-13.183378187577</v>
       </c>
       <c r="E43">
-        <v>45.82400000000001</v>
+        <v>47.98800000000001</v>
       </c>
       <c r="F43">
-        <v>88.724</v>
+        <v>90.88800000000001</v>
       </c>
       <c r="G43">
         <v>229.4</v>
@@ -4813,28 +4813,28 @@
         <v>104.883</v>
       </c>
       <c r="M43">
-        <v>4.4628172</v>
+        <v>4.5716664</v>
       </c>
       <c r="N43">
-        <v>100.4201828</v>
+        <v>100.3113336</v>
       </c>
       <c r="O43">
-        <v>10.04201828</v>
+        <v>10.03113336</v>
       </c>
       <c r="P43">
-        <v>90.37816452000001</v>
+        <v>90.28020024000001</v>
       </c>
       <c r="Q43">
-        <v>90.69516452000001</v>
+        <v>90.59720024000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2393366584280208</v>
+        <v>0.2424682069625075</v>
       </c>
       <c r="T43">
-        <v>1.183646110588774</v>
+        <v>1.202798271595747</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>23.50152276010768</v>
+        <v>22.94196269439083</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1596449600382543</v>
+        <v>0.1595205916039764</v>
       </c>
       <c r="C44">
-        <v>125.328621812423</v>
+        <v>123.163465591249</v>
       </c>
       <c r="D44">
-        <v>-13.183378187577</v>
+        <v>-13.18453440875103</v>
       </c>
       <c r="E44">
-        <v>47.98800000000001</v>
+        <v>50.15200000000001</v>
       </c>
       <c r="F44">
-        <v>90.88800000000001</v>
+        <v>93.05200000000001</v>
       </c>
       <c r="G44">
         <v>229.4</v>
@@ -4895,28 +4895,28 @@
         <v>104.883</v>
       </c>
       <c r="M44">
-        <v>4.5716664</v>
+        <v>4.6805156</v>
       </c>
       <c r="N44">
-        <v>100.3113336</v>
+        <v>100.2024844</v>
       </c>
       <c r="O44">
-        <v>10.03113336</v>
+        <v>10.02024844</v>
       </c>
       <c r="P44">
-        <v>90.28020024000001</v>
+        <v>90.18223596</v>
       </c>
       <c r="Q44">
-        <v>90.59720024000001</v>
+        <v>90.49923595999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2424682069625074</v>
+        <v>0.245709634392941</v>
       </c>
       <c r="T44">
-        <v>1.202798271595747</v>
+        <v>1.222622438252088</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>22.94196269439083</v>
+        <v>22.4084286782422</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1595205916039764</v>
+        <v>0.1593962231696985</v>
       </c>
       <c r="C45">
-        <v>123.163465591249</v>
+        <v>120.9983091672491</v>
       </c>
       <c r="D45">
-        <v>-13.18453440875103</v>
+        <v>-13.18569083275085</v>
       </c>
       <c r="E45">
-        <v>50.15200000000001</v>
+        <v>52.31600000000001</v>
       </c>
       <c r="F45">
-        <v>93.05200000000001</v>
+        <v>95.21600000000001</v>
       </c>
       <c r="G45">
         <v>229.4</v>
@@ -4977,28 +4977,28 @@
         <v>104.883</v>
       </c>
       <c r="M45">
-        <v>4.6805156</v>
+        <v>4.7893648</v>
       </c>
       <c r="N45">
-        <v>100.2024844</v>
+        <v>100.0936352</v>
       </c>
       <c r="O45">
-        <v>10.02024844</v>
+        <v>10.00936352</v>
       </c>
       <c r="P45">
-        <v>90.18223596</v>
+        <v>90.08427168</v>
       </c>
       <c r="Q45">
-        <v>90.49923595999999</v>
+        <v>90.40127167999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.245709634392941</v>
+        <v>0.2490668270887473</v>
       </c>
       <c r="T45">
-        <v>1.222622438252088</v>
+        <v>1.243154610860442</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>22.4084286782422</v>
+        <v>21.89914620828215</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1593962231696985</v>
+        <v>0.1592718547354205</v>
       </c>
       <c r="C46">
-        <v>120.9983091672491</v>
+        <v>118.8331525403701</v>
       </c>
       <c r="D46">
-        <v>-13.18569083275085</v>
+        <v>-13.18684745962986</v>
       </c>
       <c r="E46">
-        <v>52.31600000000001</v>
+        <v>54.48000000000001</v>
       </c>
       <c r="F46">
-        <v>95.21600000000001</v>
+        <v>97.38000000000001</v>
       </c>
       <c r="G46">
         <v>229.4</v>
@@ -5059,28 +5059,28 @@
         <v>104.883</v>
       </c>
       <c r="M46">
-        <v>4.7893648</v>
+        <v>4.898214</v>
       </c>
       <c r="N46">
-        <v>100.0936352</v>
+        <v>99.98478600000001</v>
       </c>
       <c r="O46">
-        <v>10.00936352</v>
+        <v>9.998478600000002</v>
       </c>
       <c r="P46">
-        <v>90.08427168</v>
+        <v>89.98630740000002</v>
       </c>
       <c r="Q46">
-        <v>90.40127167999999</v>
+        <v>90.30330740000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2490668270887473</v>
+        <v>0.2525460995189464</v>
       </c>
       <c r="T46">
-        <v>1.243154610860442</v>
+        <v>1.264433407927281</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>21.89914620828215</v>
+        <v>21.41249851476477</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1592718547354205</v>
+        <v>0.1591474863011426</v>
       </c>
       <c r="C47">
-        <v>118.8331525403701</v>
+        <v>116.6679957105586</v>
       </c>
       <c r="D47">
-        <v>-13.18684745962986</v>
+        <v>-13.18800428944145</v>
       </c>
       <c r="E47">
-        <v>54.48000000000001</v>
+        <v>56.64400000000001</v>
       </c>
       <c r="F47">
-        <v>97.38000000000001</v>
+        <v>99.54400000000001</v>
       </c>
       <c r="G47">
         <v>229.4</v>
@@ -5141,28 +5141,28 @@
         <v>104.883</v>
       </c>
       <c r="M47">
-        <v>4.898214</v>
+        <v>5.0070632</v>
       </c>
       <c r="N47">
-        <v>99.98478600000001</v>
+        <v>99.87593680000001</v>
       </c>
       <c r="O47">
-        <v>9.998478600000002</v>
+        <v>9.987593680000002</v>
       </c>
       <c r="P47">
-        <v>89.98630740000002</v>
+        <v>89.88834312</v>
       </c>
       <c r="Q47">
-        <v>90.30330740000001</v>
+        <v>90.20534311999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2525460995189464</v>
+        <v>0.2561542338910048</v>
       </c>
       <c r="T47">
-        <v>1.264433407927281</v>
+        <v>1.286500308589188</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>21.41249851476477</v>
+        <v>20.94700941661771</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1591474863011426</v>
+        <v>0.1590231178668647</v>
       </c>
       <c r="C48">
-        <v>116.6679957105586</v>
+        <v>114.502838677761</v>
       </c>
       <c r="D48">
-        <v>-13.18800428944145</v>
+        <v>-13.18916132223902</v>
       </c>
       <c r="E48">
-        <v>56.64400000000001</v>
+        <v>58.80800000000001</v>
       </c>
       <c r="F48">
-        <v>99.54400000000001</v>
+        <v>101.708</v>
       </c>
       <c r="G48">
         <v>229.4</v>
@@ -5223,28 +5223,28 @@
         <v>104.883</v>
       </c>
       <c r="M48">
-        <v>5.0070632</v>
+        <v>5.1159124</v>
       </c>
       <c r="N48">
-        <v>99.87593680000001</v>
+        <v>99.76708760000001</v>
       </c>
       <c r="O48">
-        <v>9.987593680000002</v>
+        <v>9.976708760000001</v>
       </c>
       <c r="P48">
-        <v>89.88834312</v>
+        <v>89.79037884000002</v>
       </c>
       <c r="Q48">
-        <v>90.20534311999999</v>
+        <v>90.10737884000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2561542338910048</v>
+        <v>0.2598985242771031</v>
       </c>
       <c r="T48">
-        <v>1.286500308589188</v>
+        <v>1.30939992248362</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>20.94700941661771</v>
+        <v>20.50132836520031</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1590231178668647</v>
+        <v>0.1588987494325867</v>
       </c>
       <c r="C49">
-        <v>114.502838677761</v>
+        <v>112.337681441924</v>
       </c>
       <c r="D49">
-        <v>-13.18916132223902</v>
+        <v>-13.19031855807602</v>
       </c>
       <c r="E49">
-        <v>58.80800000000001</v>
+        <v>60.97200000000002</v>
       </c>
       <c r="F49">
-        <v>101.708</v>
+        <v>103.872</v>
       </c>
       <c r="G49">
         <v>229.4</v>
@@ -5305,28 +5305,28 @@
         <v>104.883</v>
       </c>
       <c r="M49">
-        <v>5.1159124</v>
+        <v>5.224761600000001</v>
       </c>
       <c r="N49">
-        <v>99.76708760000001</v>
+        <v>99.65823840000002</v>
       </c>
       <c r="O49">
-        <v>9.976708760000001</v>
+        <v>9.965823840000002</v>
       </c>
       <c r="P49">
-        <v>89.79037884000002</v>
+        <v>89.69241456000002</v>
       </c>
       <c r="Q49">
-        <v>90.10737884000001</v>
+        <v>90.00941456000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2598985242771031</v>
+        <v>0.2637868258318976</v>
       </c>
       <c r="T49">
-        <v>1.30939992248362</v>
+        <v>1.333180290758607</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>20.50132836520031</v>
+        <v>20.07421735759197</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1588987494325867</v>
+        <v>0.1587743809983088</v>
       </c>
       <c r="C50">
-        <v>112.337681441924</v>
+        <v>110.1725240029941</v>
       </c>
       <c r="D50">
-        <v>-13.19031855807602</v>
+        <v>-13.19147599700587</v>
       </c>
       <c r="E50">
-        <v>60.972</v>
+        <v>63.136</v>
       </c>
       <c r="F50">
-        <v>103.872</v>
+        <v>106.036</v>
       </c>
       <c r="G50">
         <v>229.4</v>
@@ -5387,28 +5387,28 @@
         <v>104.883</v>
       </c>
       <c r="M50">
-        <v>5.2247616</v>
+        <v>5.3336108</v>
       </c>
       <c r="N50">
-        <v>99.65823840000002</v>
+        <v>99.54938920000001</v>
       </c>
       <c r="O50">
-        <v>9.965823840000002</v>
+        <v>9.954938920000002</v>
       </c>
       <c r="P50">
-        <v>89.69241456000002</v>
+        <v>89.59445028</v>
       </c>
       <c r="Q50">
-        <v>90.00941456000001</v>
+        <v>89.91145028</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2637868258318976</v>
+        <v>0.2678276098006055</v>
       </c>
       <c r="T50">
-        <v>1.333180290758607</v>
+        <v>1.357893222495359</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>20.07421735759198</v>
+        <v>19.664539452335</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1587743809983088</v>
+        <v>0.1586500125640309</v>
       </c>
       <c r="C51">
-        <v>110.1725240029941</v>
+        <v>108.0073663609179</v>
       </c>
       <c r="D51">
-        <v>-13.19147599700587</v>
+        <v>-13.19263363908206</v>
       </c>
       <c r="E51">
-        <v>63.136</v>
+        <v>65.30000000000001</v>
       </c>
       <c r="F51">
-        <v>106.036</v>
+        <v>108.2</v>
       </c>
       <c r="G51">
         <v>229.4</v>
@@ -5469,28 +5469,28 @@
         <v>104.883</v>
       </c>
       <c r="M51">
-        <v>5.3336108</v>
+        <v>5.44246</v>
       </c>
       <c r="N51">
-        <v>99.54938920000001</v>
+        <v>99.44054000000001</v>
       </c>
       <c r="O51">
-        <v>9.954938920000002</v>
+        <v>9.944054000000001</v>
       </c>
       <c r="P51">
-        <v>89.59445028</v>
+        <v>89.496486</v>
       </c>
       <c r="Q51">
-        <v>89.91145028</v>
+        <v>89.813486</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2678276098006055</v>
+        <v>0.2720300251280617</v>
       </c>
       <c r="T51">
-        <v>1.357893222495359</v>
+        <v>1.38359467150158</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>19.664539452335</v>
+        <v>19.2712486632883</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1586500125640309</v>
+        <v>0.1585256441297529</v>
       </c>
       <c r="C52">
-        <v>108.0073663609179</v>
+        <v>105.8422085156419</v>
       </c>
       <c r="D52">
-        <v>-13.19263363908206</v>
+        <v>-13.19379148435808</v>
       </c>
       <c r="E52">
-        <v>65.30000000000001</v>
+        <v>67.464</v>
       </c>
       <c r="F52">
-        <v>108.2</v>
+        <v>110.364</v>
       </c>
       <c r="G52">
         <v>229.4</v>
@@ -5551,28 +5551,28 @@
         <v>104.883</v>
       </c>
       <c r="M52">
-        <v>5.44246</v>
+        <v>5.551309199999999</v>
       </c>
       <c r="N52">
-        <v>99.44054000000001</v>
+        <v>99.3316908</v>
       </c>
       <c r="O52">
-        <v>9.944054000000001</v>
+        <v>9.933169080000001</v>
       </c>
       <c r="P52">
-        <v>89.496486</v>
+        <v>89.39852172000001</v>
       </c>
       <c r="Q52">
-        <v>89.813486</v>
+        <v>89.71552172</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2720300251280617</v>
+        <v>0.2764039676117407</v>
       </c>
       <c r="T52">
-        <v>1.38359467150158</v>
+        <v>1.410345159242749</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>19.2712486632883</v>
+        <v>18.8933810424395</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1585256441297529</v>
+        <v>0.158401275695475</v>
       </c>
       <c r="C53">
-        <v>105.8422085156419</v>
+        <v>103.6770504671126</v>
       </c>
       <c r="D53">
-        <v>-13.19379148435808</v>
+        <v>-13.19494953288743</v>
       </c>
       <c r="E53">
-        <v>67.464</v>
+        <v>69.62800000000001</v>
       </c>
       <c r="F53">
-        <v>110.364</v>
+        <v>112.528</v>
       </c>
       <c r="G53">
         <v>229.4</v>
@@ -5633,28 +5633,28 @@
         <v>104.883</v>
       </c>
       <c r="M53">
-        <v>5.551309199999999</v>
+        <v>5.6601584</v>
       </c>
       <c r="N53">
-        <v>99.3316908</v>
+        <v>99.22284160000001</v>
       </c>
       <c r="O53">
-        <v>9.933169080000001</v>
+        <v>9.922284160000002</v>
       </c>
       <c r="P53">
-        <v>89.39852172000001</v>
+        <v>89.30055744000001</v>
       </c>
       <c r="Q53">
-        <v>89.71552172</v>
+        <v>89.61755744</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2764039676117407</v>
+        <v>0.2809601576989063</v>
       </c>
       <c r="T53">
-        <v>1.410345159242749</v>
+        <v>1.4382102506398</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>18.8933810424395</v>
+        <v>18.53004679162336</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.158401275695475</v>
+        <v>0.1582769072611971</v>
       </c>
       <c r="C54">
-        <v>103.6770504671126</v>
+        <v>101.5118922152764</v>
       </c>
       <c r="D54">
-        <v>-13.19494953288743</v>
+        <v>-13.19610778472363</v>
       </c>
       <c r="E54">
-        <v>69.62800000000001</v>
+        <v>71.792</v>
       </c>
       <c r="F54">
-        <v>112.528</v>
+        <v>114.692</v>
       </c>
       <c r="G54">
         <v>229.4</v>
@@ -5715,28 +5715,28 @@
         <v>104.883</v>
       </c>
       <c r="M54">
-        <v>5.6601584</v>
+        <v>5.7690076</v>
       </c>
       <c r="N54">
-        <v>99.22284160000001</v>
+        <v>99.11399240000001</v>
       </c>
       <c r="O54">
-        <v>9.922284160000002</v>
+        <v>9.911399240000001</v>
       </c>
       <c r="P54">
-        <v>89.30055744000001</v>
+        <v>89.20259316000002</v>
       </c>
       <c r="Q54">
-        <v>89.61755744</v>
+        <v>89.51959316000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2809601576989063</v>
+        <v>0.2857102282153129</v>
       </c>
       <c r="T54">
-        <v>1.4382102506398</v>
+        <v>1.467261090606939</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>18.53004679162336</v>
+        <v>18.18042326725311</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1582769072611971</v>
+        <v>0.1581525388269192</v>
       </c>
       <c r="C55">
-        <v>101.5118922152764</v>
+        <v>99.34673376007977</v>
       </c>
       <c r="D55">
-        <v>-13.19610778472363</v>
+        <v>-13.19726623992022</v>
       </c>
       <c r="E55">
-        <v>71.792</v>
+        <v>73.95600000000002</v>
       </c>
       <c r="F55">
-        <v>114.692</v>
+        <v>116.856</v>
       </c>
       <c r="G55">
         <v>229.4</v>
@@ -5797,28 +5797,28 @@
         <v>104.883</v>
       </c>
       <c r="M55">
-        <v>5.7690076</v>
+        <v>5.8778568</v>
       </c>
       <c r="N55">
-        <v>99.11399240000001</v>
+        <v>99.00514320000001</v>
       </c>
       <c r="O55">
-        <v>9.911399240000001</v>
+        <v>9.900514320000001</v>
       </c>
       <c r="P55">
-        <v>89.20259316000002</v>
+        <v>89.10462888000001</v>
       </c>
       <c r="Q55">
-        <v>89.51959316000001</v>
+        <v>89.42162888</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2857102282153129</v>
+        <v>0.2906668235367809</v>
       </c>
       <c r="T55">
-        <v>1.467261090606939</v>
+        <v>1.497575010572649</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>18.18042326725311</v>
+        <v>17.84374876230397</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1581525388269192</v>
+        <v>0.1580281703926413</v>
       </c>
       <c r="C56">
-        <v>99.34673376007977</v>
+        <v>97.18157510146921</v>
       </c>
       <c r="D56">
-        <v>-13.19726623992022</v>
+        <v>-13.19842489853078</v>
       </c>
       <c r="E56">
-        <v>73.95600000000002</v>
+        <v>76.12</v>
       </c>
       <c r="F56">
-        <v>116.856</v>
+        <v>119.02</v>
       </c>
       <c r="G56">
         <v>229.4</v>
@@ -5879,28 +5879,28 @@
         <v>104.883</v>
       </c>
       <c r="M56">
-        <v>5.8778568</v>
+        <v>5.986706</v>
       </c>
       <c r="N56">
-        <v>99.00514320000001</v>
+        <v>98.89629400000001</v>
       </c>
       <c r="O56">
-        <v>9.900514320000001</v>
+        <v>9.889629400000002</v>
       </c>
       <c r="P56">
-        <v>89.10462888000001</v>
+        <v>89.00666460000001</v>
       </c>
       <c r="Q56">
-        <v>89.42162888</v>
+        <v>89.3236646</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2906668235367809</v>
+        <v>0.2958437119836473</v>
       </c>
       <c r="T56">
-        <v>1.497575010572649</v>
+        <v>1.529236215870168</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>17.84374876230397</v>
+        <v>17.51931696662572</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1580281703926413</v>
+        <v>0.1579038019583633</v>
       </c>
       <c r="C57">
-        <v>97.18157510146921</v>
+        <v>95.01641623939112</v>
       </c>
       <c r="D57">
-        <v>-13.19842489853078</v>
+        <v>-13.19958376060887</v>
       </c>
       <c r="E57">
-        <v>76.12</v>
+        <v>78.28400000000002</v>
       </c>
       <c r="F57">
-        <v>119.02</v>
+        <v>121.184</v>
       </c>
       <c r="G57">
         <v>229.4</v>
@@ -5961,28 +5961,28 @@
         <v>104.883</v>
       </c>
       <c r="M57">
-        <v>5.986706</v>
+        <v>6.095555200000001</v>
       </c>
       <c r="N57">
-        <v>98.89629400000001</v>
+        <v>98.7874448</v>
       </c>
       <c r="O57">
-        <v>9.889629400000002</v>
+        <v>9.878744480000002</v>
       </c>
       <c r="P57">
-        <v>89.00666460000001</v>
+        <v>88.90870032000001</v>
       </c>
       <c r="Q57">
-        <v>89.3236646</v>
+        <v>89.22570032</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2958437119836473</v>
+        <v>0.3012559135417348</v>
       </c>
       <c r="T57">
-        <v>1.529236215870168</v>
+        <v>1.562336566863028</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>17.51931696662572</v>
+        <v>17.20647202079312</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1579038019583633</v>
+        <v>0.1577794335240854</v>
       </c>
       <c r="C58">
-        <v>95.01641623939112</v>
+        <v>92.85125717379188</v>
       </c>
       <c r="D58">
-        <v>-13.19958376060887</v>
+        <v>-13.20074282620811</v>
       </c>
       <c r="E58">
-        <v>78.28400000000002</v>
+        <v>80.44800000000001</v>
       </c>
       <c r="F58">
-        <v>121.184</v>
+        <v>123.348</v>
       </c>
       <c r="G58">
         <v>229.4</v>
@@ -6043,28 +6043,28 @@
         <v>104.883</v>
       </c>
       <c r="M58">
-        <v>6.095555200000001</v>
+        <v>6.2044044</v>
       </c>
       <c r="N58">
-        <v>98.7874448</v>
+        <v>98.67859560000001</v>
       </c>
       <c r="O58">
-        <v>9.878744480000002</v>
+        <v>9.867859560000001</v>
       </c>
       <c r="P58">
-        <v>88.90870032000001</v>
+        <v>88.81073604000001</v>
       </c>
       <c r="Q58">
-        <v>89.22570032</v>
+        <v>89.12773604</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3012559135417348</v>
+        <v>0.3069198454048498</v>
       </c>
       <c r="T58">
-        <v>1.562336566863028</v>
+        <v>1.596976469064859</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>17.20647202079312</v>
+        <v>16.90460409060377</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1577794335240854</v>
+        <v>0.1576550650898075</v>
       </c>
       <c r="C59">
-        <v>92.85125717379188</v>
+        <v>90.68609790461788</v>
       </c>
       <c r="D59">
-        <v>-13.20074282620811</v>
+        <v>-13.2019020953821</v>
       </c>
       <c r="E59">
-        <v>80.44800000000001</v>
+        <v>82.61200000000002</v>
       </c>
       <c r="F59">
-        <v>123.348</v>
+        <v>125.512</v>
       </c>
       <c r="G59">
         <v>229.4</v>
@@ -6125,28 +6125,28 @@
         <v>104.883</v>
       </c>
       <c r="M59">
-        <v>6.2044044</v>
+        <v>6.3132536</v>
       </c>
       <c r="N59">
-        <v>98.67859560000001</v>
+        <v>98.56974640000001</v>
       </c>
       <c r="O59">
-        <v>9.867859560000001</v>
+        <v>9.856974640000002</v>
       </c>
       <c r="P59">
-        <v>88.81073604000001</v>
+        <v>88.71277176000001</v>
       </c>
       <c r="Q59">
-        <v>89.12773604</v>
+        <v>89.02977176</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3069198454048498</v>
+        <v>0.3128534883090655</v>
       </c>
       <c r="T59">
-        <v>1.596976469064859</v>
+        <v>1.633265890419159</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>16.90460409060377</v>
+        <v>16.61314539938646</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1576550650898075</v>
+        <v>0.1575306966555295</v>
       </c>
       <c r="C60">
-        <v>90.6860979046179</v>
+        <v>88.52093843181551</v>
       </c>
       <c r="D60">
-        <v>-13.2019020953821</v>
+        <v>-13.20306156818449</v>
       </c>
       <c r="E60">
-        <v>82.61199999999999</v>
+        <v>84.77600000000001</v>
       </c>
       <c r="F60">
-        <v>125.512</v>
+        <v>127.676</v>
       </c>
       <c r="G60">
         <v>229.4</v>
@@ -6207,28 +6207,28 @@
         <v>104.883</v>
       </c>
       <c r="M60">
-        <v>6.313253599999999</v>
+        <v>6.422102799999999</v>
       </c>
       <c r="N60">
-        <v>98.56974640000001</v>
+        <v>98.46089720000001</v>
       </c>
       <c r="O60">
-        <v>9.856974640000002</v>
+        <v>9.846089720000002</v>
       </c>
       <c r="P60">
-        <v>88.71277176000001</v>
+        <v>88.61480748</v>
       </c>
       <c r="Q60">
-        <v>89.02977176</v>
+        <v>88.93180747999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3128534883090655</v>
+        <v>0.3190765772086087</v>
       </c>
       <c r="T60">
-        <v>1.633265890419158</v>
+        <v>1.671325527449277</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>16.61314539938646</v>
+        <v>16.33156666380364</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1575306966555295</v>
+        <v>0.1574063282212516</v>
       </c>
       <c r="C61">
-        <v>88.52093843181551</v>
+        <v>86.35577875533107</v>
       </c>
       <c r="D61">
-        <v>-13.20306156818449</v>
+        <v>-13.20422124466894</v>
       </c>
       <c r="E61">
-        <v>84.77600000000001</v>
+        <v>86.94</v>
       </c>
       <c r="F61">
-        <v>127.676</v>
+        <v>129.84</v>
       </c>
       <c r="G61">
         <v>229.4</v>
@@ -6289,28 +6289,28 @@
         <v>104.883</v>
       </c>
       <c r="M61">
-        <v>6.422102799999999</v>
+        <v>6.530952</v>
       </c>
       <c r="N61">
-        <v>98.46089720000001</v>
+        <v>98.35204800000001</v>
       </c>
       <c r="O61">
-        <v>9.846089720000002</v>
+        <v>9.835204800000001</v>
       </c>
       <c r="P61">
-        <v>88.61480748</v>
+        <v>88.51684320000001</v>
       </c>
       <c r="Q61">
-        <v>88.93180747999999</v>
+        <v>88.8338432</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3190765772086087</v>
+        <v>0.325610820553129</v>
       </c>
       <c r="T61">
-        <v>1.671325527449277</v>
+        <v>1.711288146330901</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>16.33156666380364</v>
+        <v>16.05937388607358</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1574063282212516</v>
+        <v>0.1572819597869737</v>
       </c>
       <c r="C62">
-        <v>86.35577875533107</v>
+        <v>84.19061887511091</v>
       </c>
       <c r="D62">
-        <v>-13.20422124466894</v>
+        <v>-13.20538112488911</v>
       </c>
       <c r="E62">
-        <v>86.94</v>
+        <v>89.10399999999998</v>
       </c>
       <c r="F62">
-        <v>129.84</v>
+        <v>132.004</v>
       </c>
       <c r="G62">
         <v>229.4</v>
@@ -6371,28 +6371,28 @@
         <v>104.883</v>
       </c>
       <c r="M62">
-        <v>6.530952</v>
+        <v>6.639801199999999</v>
       </c>
       <c r="N62">
-        <v>98.35204800000001</v>
+        <v>98.24319880000002</v>
       </c>
       <c r="O62">
-        <v>9.835204800000001</v>
+        <v>9.824319880000003</v>
       </c>
       <c r="P62">
-        <v>88.51684320000001</v>
+        <v>88.41887892000001</v>
       </c>
       <c r="Q62">
-        <v>88.8338432</v>
+        <v>88.73587892</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.325610820553129</v>
+        <v>0.3324801532999326</v>
       </c>
       <c r="T62">
-        <v>1.711288146330901</v>
+        <v>1.753300130283379</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>16.05937388607358</v>
+        <v>15.79610546171172</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1572819597869737</v>
+        <v>0.1571575913526957</v>
       </c>
       <c r="C63">
-        <v>84.19061887511091</v>
+        <v>82.0254587911013</v>
       </c>
       <c r="D63">
-        <v>-13.20538112488911</v>
+        <v>-13.2065412088987</v>
       </c>
       <c r="E63">
-        <v>89.10399999999998</v>
+        <v>91.268</v>
       </c>
       <c r="F63">
-        <v>132.004</v>
+        <v>134.168</v>
       </c>
       <c r="G63">
         <v>229.4</v>
@@ -6453,28 +6453,28 @@
         <v>104.883</v>
       </c>
       <c r="M63">
-        <v>6.639801199999999</v>
+        <v>6.7486504</v>
       </c>
       <c r="N63">
-        <v>98.24319880000002</v>
+        <v>98.13434960000001</v>
       </c>
       <c r="O63">
-        <v>9.824319880000003</v>
+        <v>9.813434960000002</v>
       </c>
       <c r="P63">
-        <v>88.41887892000001</v>
+        <v>88.32091464000001</v>
       </c>
       <c r="Q63">
-        <v>88.73587892</v>
+        <v>88.63791464000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3324801532999326</v>
+        <v>0.3397110298755152</v>
       </c>
       <c r="T63">
-        <v>1.753300130283379</v>
+        <v>1.797523271285986</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>15.79610546171172</v>
+        <v>15.54132956716798</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1571575913526957</v>
+        <v>0.1570332229184178</v>
       </c>
       <c r="C64">
-        <v>82.0254587911013</v>
+        <v>79.86029850324857</v>
       </c>
       <c r="D64">
-        <v>-13.2065412088987</v>
+        <v>-13.20770149675143</v>
       </c>
       <c r="E64">
-        <v>91.268</v>
+        <v>93.43199999999999</v>
       </c>
       <c r="F64">
-        <v>134.168</v>
+        <v>136.332</v>
       </c>
       <c r="G64">
         <v>229.4</v>
@@ -6535,28 +6535,28 @@
         <v>104.883</v>
       </c>
       <c r="M64">
-        <v>6.7486504</v>
+        <v>6.8574996</v>
       </c>
       <c r="N64">
-        <v>98.13434960000001</v>
+        <v>98.02550040000001</v>
       </c>
       <c r="O64">
-        <v>9.813434960000002</v>
+        <v>9.802550040000002</v>
       </c>
       <c r="P64">
-        <v>88.32091464000001</v>
+        <v>88.22295036000001</v>
       </c>
       <c r="Q64">
-        <v>88.63791464000001</v>
+        <v>88.53995036000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3397110298755152</v>
+        <v>0.3473327646443725</v>
       </c>
       <c r="T64">
-        <v>1.797523271285986</v>
+        <v>1.844136852342788</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>15.54132956716798</v>
+        <v>15.29464179626055</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1570332229184178</v>
+        <v>0.1569088544841399</v>
       </c>
       <c r="C65">
-        <v>79.86029850324857</v>
+        <v>77.69513801149895</v>
       </c>
       <c r="D65">
-        <v>-13.20770149675143</v>
+        <v>-13.20886198850103</v>
       </c>
       <c r="E65">
-        <v>93.43199999999999</v>
+        <v>95.596</v>
       </c>
       <c r="F65">
-        <v>136.332</v>
+        <v>138.496</v>
       </c>
       <c r="G65">
         <v>229.4</v>
@@ -6617,28 +6617,28 @@
         <v>104.883</v>
       </c>
       <c r="M65">
-        <v>6.8574996</v>
+        <v>6.9663488</v>
       </c>
       <c r="N65">
-        <v>98.02550040000001</v>
+        <v>97.9166512</v>
       </c>
       <c r="O65">
-        <v>9.802550040000002</v>
+        <v>9.791665120000001</v>
       </c>
       <c r="P65">
-        <v>88.22295036000001</v>
+        <v>88.12498608</v>
       </c>
       <c r="Q65">
-        <v>88.53995036000001</v>
+        <v>88.44198607999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3473327646443725</v>
+        <v>0.3553779291226108</v>
       </c>
       <c r="T65">
-        <v>1.844136852342788</v>
+        <v>1.893340076791636</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>15.29464179626055</v>
+        <v>15.05566301819398</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1569088544841399</v>
+        <v>0.156784486049862</v>
       </c>
       <c r="C66">
-        <v>77.69513801149895</v>
+        <v>75.52997731579876</v>
       </c>
       <c r="D66">
-        <v>-13.20886198850103</v>
+        <v>-13.21002268420125</v>
       </c>
       <c r="E66">
-        <v>95.596</v>
+        <v>97.75999999999999</v>
       </c>
       <c r="F66">
-        <v>138.496</v>
+        <v>140.66</v>
       </c>
       <c r="G66">
         <v>229.4</v>
@@ -6699,28 +6699,28 @@
         <v>104.883</v>
       </c>
       <c r="M66">
-        <v>6.9663488</v>
+        <v>7.075197999999999</v>
       </c>
       <c r="N66">
-        <v>97.9166512</v>
+        <v>97.80780200000001</v>
       </c>
       <c r="O66">
-        <v>9.791665120000001</v>
+        <v>9.780780200000002</v>
       </c>
       <c r="P66">
-        <v>88.12498608</v>
+        <v>88.0270218</v>
       </c>
       <c r="Q66">
-        <v>88.44198607999999</v>
+        <v>88.34402179999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3553779291226108</v>
+        <v>0.36388281728532</v>
       </c>
       <c r="T66">
-        <v>1.893340076791636</v>
+        <v>1.945354914066131</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>15.05566301819398</v>
+        <v>14.82403743329869</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.156784486049862</v>
+        <v>0.156660117615584</v>
       </c>
       <c r="C67">
-        <v>75.52997731579876</v>
+        <v>73.36481641609413</v>
       </c>
       <c r="D67">
-        <v>-13.21002268420125</v>
+        <v>-13.21118358390585</v>
       </c>
       <c r="E67">
-        <v>97.75999999999999</v>
+        <v>99.92400000000001</v>
       </c>
       <c r="F67">
-        <v>140.66</v>
+        <v>142.824</v>
       </c>
       <c r="G67">
         <v>229.4</v>
@@ -6781,28 +6781,28 @@
         <v>104.883</v>
       </c>
       <c r="M67">
-        <v>7.075197999999999</v>
+        <v>7.1840472</v>
       </c>
       <c r="N67">
-        <v>97.80780200000001</v>
+        <v>97.69895280000001</v>
       </c>
       <c r="O67">
-        <v>9.780780200000002</v>
+        <v>9.769895280000002</v>
       </c>
       <c r="P67">
-        <v>88.0270218</v>
+        <v>87.92905752000001</v>
       </c>
       <c r="Q67">
-        <v>88.34402179999999</v>
+        <v>88.24605752000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.36388281728532</v>
+        <v>0.3728879929870119</v>
       </c>
       <c r="T67">
-        <v>1.945354914066131</v>
+        <v>2.000429447650891</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>14.82403743329869</v>
+        <v>14.59943080552144</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.156660117615584</v>
+        <v>0.1565357491813061</v>
       </c>
       <c r="C68">
-        <v>73.36481641609413</v>
+        <v>71.19965531233137</v>
       </c>
       <c r="D68">
-        <v>-13.21118358390585</v>
+        <v>-13.21234468766863</v>
       </c>
       <c r="E68">
-        <v>99.92400000000001</v>
+        <v>102.088</v>
       </c>
       <c r="F68">
-        <v>142.824</v>
+        <v>144.988</v>
       </c>
       <c r="G68">
         <v>229.4</v>
@@ -6863,28 +6863,28 @@
         <v>104.883</v>
       </c>
       <c r="M68">
-        <v>7.1840472</v>
+        <v>7.2928964</v>
       </c>
       <c r="N68">
-        <v>97.69895280000001</v>
+        <v>97.59010360000001</v>
       </c>
       <c r="O68">
-        <v>9.769895280000002</v>
+        <v>9.759010360000001</v>
       </c>
       <c r="P68">
-        <v>87.92905752000001</v>
+        <v>87.83109324</v>
       </c>
       <c r="Q68">
-        <v>88.24605752000001</v>
+        <v>88.14809323999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3728879929870119</v>
+        <v>0.3824389369130489</v>
       </c>
       <c r="T68">
-        <v>2.000429447650891</v>
+        <v>2.05884183175594</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>14.59943080552144</v>
+        <v>14.38152885320022</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1565357491813061</v>
+        <v>0.1564113807470282</v>
       </c>
       <c r="C69">
-        <v>71.19965531233137</v>
+        <v>69.0344940044566</v>
       </c>
       <c r="D69">
-        <v>-13.21234468766863</v>
+        <v>-13.21350599554339</v>
       </c>
       <c r="E69">
-        <v>102.088</v>
+        <v>104.252</v>
       </c>
       <c r="F69">
-        <v>144.988</v>
+        <v>147.152</v>
       </c>
       <c r="G69">
         <v>229.4</v>
@@ -6945,28 +6945,28 @@
         <v>104.883</v>
       </c>
       <c r="M69">
-        <v>7.2928964</v>
+        <v>7.401745600000001</v>
       </c>
       <c r="N69">
-        <v>97.59010360000001</v>
+        <v>97.48125440000001</v>
       </c>
       <c r="O69">
-        <v>9.759010360000001</v>
+        <v>9.748125440000003</v>
       </c>
       <c r="P69">
-        <v>87.83109324</v>
+        <v>87.73312896000002</v>
       </c>
       <c r="Q69">
-        <v>88.14809323999999</v>
+        <v>88.05012896000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3824389369130489</v>
+        <v>0.3925868148344632</v>
       </c>
       <c r="T69">
-        <v>2.05884183175594</v>
+        <v>2.120904989867554</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>14.38152885320022</v>
+        <v>14.17003578182963</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1564113807470282</v>
+        <v>0.1562870123127502</v>
       </c>
       <c r="C70">
-        <v>69.0344940044566</v>
+        <v>66.86933249241602</v>
       </c>
       <c r="D70">
-        <v>-13.21350599554339</v>
+        <v>-13.21466750758397</v>
       </c>
       <c r="E70">
-        <v>104.252</v>
+        <v>106.416</v>
       </c>
       <c r="F70">
-        <v>147.152</v>
+        <v>149.316</v>
       </c>
       <c r="G70">
         <v>229.4</v>
@@ -7027,28 +7027,28 @@
         <v>104.883</v>
       </c>
       <c r="M70">
-        <v>7.401745600000001</v>
+        <v>7.5105948</v>
       </c>
       <c r="N70">
-        <v>97.48125440000001</v>
+        <v>97.3724052</v>
       </c>
       <c r="O70">
-        <v>9.748125440000003</v>
+        <v>9.73724052</v>
       </c>
       <c r="P70">
-        <v>87.73312896000002</v>
+        <v>87.63516468</v>
       </c>
       <c r="Q70">
-        <v>88.05012896000001</v>
+        <v>87.95216468</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3925868148344632</v>
+        <v>0.403389394557259</v>
       </c>
       <c r="T70">
-        <v>2.120904989867554</v>
+        <v>2.186972222696046</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>14.17003578182963</v>
+        <v>13.96467294441181</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1562870123127502</v>
+        <v>0.1561626438784723</v>
       </c>
       <c r="C71">
-        <v>66.86933249241602</v>
+        <v>64.70417077615579</v>
       </c>
       <c r="D71">
-        <v>-13.21466750758397</v>
+        <v>-13.2158292238442</v>
       </c>
       <c r="E71">
-        <v>106.416</v>
+        <v>108.58</v>
       </c>
       <c r="F71">
-        <v>149.316</v>
+        <v>151.48</v>
       </c>
       <c r="G71">
         <v>229.4</v>
@@ -7109,28 +7109,28 @@
         <v>104.883</v>
       </c>
       <c r="M71">
-        <v>7.5105948</v>
+        <v>7.619444000000001</v>
       </c>
       <c r="N71">
-        <v>97.3724052</v>
+        <v>97.26355600000001</v>
       </c>
       <c r="O71">
-        <v>9.73724052</v>
+        <v>9.726355600000002</v>
       </c>
       <c r="P71">
-        <v>87.63516468</v>
+        <v>87.5372004</v>
       </c>
       <c r="Q71">
-        <v>87.95216468</v>
+        <v>87.8542004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.403389394557259</v>
+        <v>0.4149121462615745</v>
       </c>
       <c r="T71">
-        <v>2.186972222696046</v>
+        <v>2.257443937713104</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>13.96467294441181</v>
+        <v>13.76517761663449</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1561626438784723</v>
+        <v>0.1560382754441944</v>
       </c>
       <c r="C72">
-        <v>64.70417077615579</v>
+        <v>62.53900885562203</v>
       </c>
       <c r="D72">
-        <v>-13.2158292238442</v>
+        <v>-13.21699114437795</v>
       </c>
       <c r="E72">
-        <v>108.58</v>
+        <v>110.744</v>
       </c>
       <c r="F72">
-        <v>151.48</v>
+        <v>153.644</v>
       </c>
       <c r="G72">
         <v>229.4</v>
@@ -7191,28 +7191,28 @@
         <v>104.883</v>
       </c>
       <c r="M72">
-        <v>7.619444000000001</v>
+        <v>7.728293200000001</v>
       </c>
       <c r="N72">
-        <v>97.26355600000001</v>
+        <v>97.15470680000001</v>
       </c>
       <c r="O72">
-        <v>9.726355600000002</v>
+        <v>9.715470680000003</v>
       </c>
       <c r="P72">
-        <v>87.5372004</v>
+        <v>87.43923612</v>
       </c>
       <c r="Q72">
-        <v>87.8542004</v>
+        <v>87.75623612</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4149121462615745</v>
+        <v>0.4272295704972223</v>
       </c>
       <c r="T72">
-        <v>2.257443937713104</v>
+        <v>2.332775771007202</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>13.76517761663449</v>
+        <v>13.57130187555514</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1560382754441944</v>
+        <v>0.1559139070099165</v>
       </c>
       <c r="C73">
-        <v>62.53900885562206</v>
+        <v>60.3738467307609</v>
       </c>
       <c r="D73">
-        <v>-13.21699114437795</v>
+        <v>-13.2181532692391</v>
       </c>
       <c r="E73">
-        <v>110.744</v>
+        <v>112.908</v>
       </c>
       <c r="F73">
-        <v>153.644</v>
+        <v>155.808</v>
       </c>
       <c r="G73">
         <v>229.4</v>
@@ -7273,28 +7273,28 @@
         <v>104.883</v>
       </c>
       <c r="M73">
-        <v>7.7282932</v>
+        <v>7.837142399999999</v>
       </c>
       <c r="N73">
-        <v>97.15470680000001</v>
+        <v>97.04585760000001</v>
       </c>
       <c r="O73">
-        <v>9.715470680000003</v>
+        <v>9.704585760000001</v>
       </c>
       <c r="P73">
-        <v>87.43923612</v>
+        <v>87.34127184</v>
       </c>
       <c r="Q73">
-        <v>87.75623612</v>
+        <v>87.65827184</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4272295704972222</v>
+        <v>0.4404268107497017</v>
       </c>
       <c r="T73">
-        <v>2.332775771007201</v>
+        <v>2.41348844953659</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>13.57130187555514</v>
+        <v>13.38281157172798</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1559139070099165</v>
+        <v>0.1557895385756385</v>
       </c>
       <c r="C74">
-        <v>60.3738467307609</v>
+        <v>58.20868440151844</v>
       </c>
       <c r="D74">
-        <v>-13.2181532692391</v>
+        <v>-13.21931559848156</v>
       </c>
       <c r="E74">
-        <v>112.908</v>
+        <v>115.072</v>
       </c>
       <c r="F74">
-        <v>155.808</v>
+        <v>157.972</v>
       </c>
       <c r="G74">
         <v>229.4</v>
@@ -7355,28 +7355,28 @@
         <v>104.883</v>
       </c>
       <c r="M74">
-        <v>7.837142399999999</v>
+        <v>7.9459916</v>
       </c>
       <c r="N74">
-        <v>97.04585760000001</v>
+        <v>96.93700840000001</v>
       </c>
       <c r="O74">
-        <v>9.704585760000001</v>
+        <v>9.693700840000002</v>
       </c>
       <c r="P74">
-        <v>87.34127184</v>
+        <v>87.24330756000001</v>
       </c>
       <c r="Q74">
-        <v>87.65827184</v>
+        <v>87.56030756</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4404268107497017</v>
+        <v>0.4546016243542169</v>
       </c>
       <c r="T74">
-        <v>2.41348844953659</v>
+        <v>2.500179844994083</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>13.38281157172798</v>
+        <v>13.1994853858139</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1557895385756385</v>
+        <v>0.1556651701413606</v>
       </c>
       <c r="C75">
-        <v>58.20868440151844</v>
+        <v>56.04352186784075</v>
       </c>
       <c r="D75">
-        <v>-13.21931559848156</v>
+        <v>-13.22047813215925</v>
       </c>
       <c r="E75">
-        <v>115.072</v>
+        <v>117.236</v>
       </c>
       <c r="F75">
-        <v>157.972</v>
+        <v>160.136</v>
       </c>
       <c r="G75">
         <v>229.4</v>
@@ -7437,28 +7437,28 @@
         <v>104.883</v>
       </c>
       <c r="M75">
-        <v>7.9459916</v>
+        <v>8.054840799999999</v>
       </c>
       <c r="N75">
-        <v>96.93700840000001</v>
+        <v>96.82815920000002</v>
       </c>
       <c r="O75">
-        <v>9.693700840000002</v>
+        <v>9.682815920000003</v>
       </c>
       <c r="P75">
-        <v>87.24330756000001</v>
+        <v>87.14534328000002</v>
       </c>
       <c r="Q75">
-        <v>87.56030756</v>
+        <v>87.46234328000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4546016243542169</v>
+        <v>0.4698668082360024</v>
       </c>
       <c r="T75">
-        <v>2.500179844994083</v>
+        <v>2.593539809332921</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>13.1994853858139</v>
+        <v>13.02111396168128</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1556651701413606</v>
+        <v>0.1565533017070827</v>
       </c>
       <c r="C76">
-        <v>56.04352186784075</v>
+        <v>53.88781919508997</v>
       </c>
       <c r="D76">
-        <v>-13.22047813215925</v>
+        <v>-13.21218080491002</v>
       </c>
       <c r="E76">
-        <v>117.236</v>
+        <v>119.4</v>
       </c>
       <c r="F76">
-        <v>160.136</v>
+        <v>162.3</v>
       </c>
       <c r="G76">
         <v>229.4</v>
@@ -7519,45 +7519,45 @@
         <v>104.883</v>
       </c>
       <c r="M76">
-        <v>8.054840799999999</v>
+        <v>8.40714</v>
       </c>
       <c r="N76">
-        <v>96.82815920000002</v>
+        <v>96.47586000000001</v>
       </c>
       <c r="O76">
-        <v>9.682815920000003</v>
+        <v>9.647586000000002</v>
       </c>
       <c r="P76">
-        <v>87.14534328000002</v>
+        <v>86.82827400000001</v>
       </c>
       <c r="Q76">
-        <v>87.46234328000001</v>
+        <v>87.145274</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4698668082360024</v>
+        <v>0.4863532068283308</v>
       </c>
       <c r="T76">
-        <v>2.593539809332921</v>
+        <v>2.694368570818866</v>
       </c>
       <c r="U76">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V76">
         <v>0.1</v>
       </c>
       <c r="W76">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y76">
-        <v>13.02111396168128</v>
+        <v>12.47546728138225</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1565533017070827</v>
+        <v>0.1564424332728048</v>
       </c>
       <c r="C77">
-        <v>53.88781919508997</v>
+        <v>51.72278398093755</v>
       </c>
       <c r="D77">
-        <v>-13.21218080491002</v>
+        <v>-13.21321601906245</v>
       </c>
       <c r="E77">
-        <v>119.4</v>
+        <v>121.564</v>
       </c>
       <c r="F77">
-        <v>162.3</v>
+        <v>164.464</v>
       </c>
       <c r="G77">
         <v>229.4</v>
@@ -7601,28 +7601,28 @@
         <v>104.883</v>
       </c>
       <c r="M77">
-        <v>8.40714</v>
+        <v>8.519235199999999</v>
       </c>
       <c r="N77">
-        <v>96.47586000000001</v>
+        <v>96.36376480000001</v>
       </c>
       <c r="O77">
-        <v>9.647586000000002</v>
+        <v>9.636376480000003</v>
       </c>
       <c r="P77">
-        <v>86.82827400000001</v>
+        <v>86.72738832000002</v>
       </c>
       <c r="Q77">
-        <v>87.145274</v>
+        <v>87.04438832000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4863532068283308</v>
+        <v>0.50421347197002</v>
       </c>
       <c r="T77">
-        <v>2.694368570818866</v>
+        <v>2.803599729095307</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>12.47546728138225</v>
+        <v>12.31131639610091</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1564424332728048</v>
+        <v>0.1563315648385268</v>
       </c>
       <c r="C78">
-        <v>51.72278398093755</v>
+        <v>49.5577486045481</v>
       </c>
       <c r="D78">
-        <v>-13.21321601906245</v>
+        <v>-13.21425139545189</v>
       </c>
       <c r="E78">
-        <v>121.564</v>
+        <v>123.728</v>
       </c>
       <c r="F78">
-        <v>164.464</v>
+        <v>166.628</v>
       </c>
       <c r="G78">
         <v>229.4</v>
@@ -7683,28 +7683,28 @@
         <v>104.883</v>
       </c>
       <c r="M78">
-        <v>8.519235199999999</v>
+        <v>8.631330400000001</v>
       </c>
       <c r="N78">
-        <v>96.36376480000001</v>
+        <v>96.25166960000001</v>
       </c>
       <c r="O78">
-        <v>9.636376480000003</v>
+        <v>9.625166960000001</v>
       </c>
       <c r="P78">
-        <v>86.72738832000002</v>
+        <v>86.62650264000001</v>
       </c>
       <c r="Q78">
-        <v>87.04438832000001</v>
+        <v>86.94350264000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.50421347197002</v>
+        <v>0.5236268036457689</v>
       </c>
       <c r="T78">
-        <v>2.803599729095307</v>
+        <v>2.922329248961003</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>12.31131639610091</v>
+        <v>12.15142917017752</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1563315648385268</v>
+        <v>0.1562206964042489</v>
       </c>
       <c r="C79">
-        <v>49.5577486045481</v>
+        <v>47.39271306588353</v>
       </c>
       <c r="D79">
-        <v>-13.21425139545189</v>
+        <v>-13.21528693411647</v>
       </c>
       <c r="E79">
-        <v>123.728</v>
+        <v>125.892</v>
       </c>
       <c r="F79">
-        <v>166.628</v>
+        <v>168.792</v>
       </c>
       <c r="G79">
         <v>229.4</v>
@@ -7765,28 +7765,28 @@
         <v>104.883</v>
       </c>
       <c r="M79">
-        <v>8.631330400000001</v>
+        <v>8.7434256</v>
       </c>
       <c r="N79">
-        <v>96.25166960000001</v>
+        <v>96.13957440000001</v>
       </c>
       <c r="O79">
-        <v>9.625166960000001</v>
+        <v>9.613957440000002</v>
       </c>
       <c r="P79">
-        <v>86.62650264000001</v>
+        <v>86.52561696000001</v>
       </c>
       <c r="Q79">
-        <v>86.94350264000001</v>
+        <v>86.84261696</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5236268036457689</v>
+        <v>0.544804983655677</v>
       </c>
       <c r="T79">
-        <v>2.922329248961003</v>
+        <v>3.051852361541763</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>12.15142917017752</v>
+        <v>11.99564161671371</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1562206964042489</v>
+        <v>0.156109827969971</v>
       </c>
       <c r="C80">
-        <v>47.39271306588353</v>
+        <v>45.22767736490565</v>
       </c>
       <c r="D80">
-        <v>-13.21528693411647</v>
+        <v>-13.21632263509436</v>
       </c>
       <c r="E80">
-        <v>125.892</v>
+        <v>128.056</v>
       </c>
       <c r="F80">
-        <v>168.792</v>
+        <v>170.956</v>
       </c>
       <c r="G80">
         <v>229.4</v>
@@ -7847,28 +7847,28 @@
         <v>104.883</v>
       </c>
       <c r="M80">
-        <v>8.7434256</v>
+        <v>8.855520800000001</v>
       </c>
       <c r="N80">
-        <v>96.13957440000001</v>
+        <v>96.02747920000002</v>
       </c>
       <c r="O80">
-        <v>9.613957440000002</v>
+        <v>9.602747920000002</v>
       </c>
       <c r="P80">
-        <v>86.52561696000001</v>
+        <v>86.42473128000002</v>
       </c>
       <c r="Q80">
-        <v>86.84261696</v>
+        <v>86.74173128000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.544804983655677</v>
+        <v>0.5680001331903382</v>
       </c>
       <c r="T80">
-        <v>3.051852361541763</v>
+        <v>3.193711008654023</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>11.99564161671371</v>
+        <v>11.84379805194518</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.156109827969971</v>
+        <v>0.1559989595356931</v>
       </c>
       <c r="C81">
-        <v>45.22767736490565</v>
+        <v>43.06264150157631</v>
       </c>
       <c r="D81">
-        <v>-13.21632263509436</v>
+        <v>-13.2173584984237</v>
       </c>
       <c r="E81">
-        <v>128.056</v>
+        <v>130.22</v>
       </c>
       <c r="F81">
-        <v>170.956</v>
+        <v>173.12</v>
       </c>
       <c r="G81">
         <v>229.4</v>
@@ -7929,28 +7929,28 @@
         <v>104.883</v>
       </c>
       <c r="M81">
-        <v>8.855520800000001</v>
+        <v>8.967616</v>
       </c>
       <c r="N81">
-        <v>96.02747920000002</v>
+        <v>95.91538400000002</v>
       </c>
       <c r="O81">
-        <v>9.602747920000002</v>
+        <v>9.591538400000003</v>
       </c>
       <c r="P81">
-        <v>86.42473128000002</v>
+        <v>86.32384560000001</v>
       </c>
       <c r="Q81">
-        <v>86.74173128000001</v>
+        <v>86.64084560000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5680001331903382</v>
+        <v>0.5935147976784655</v>
       </c>
       <c r="T81">
-        <v>3.193711008654023</v>
+        <v>3.34975552047751</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>11.84379805194518</v>
+        <v>11.69575057629586</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1559989595356931</v>
+        <v>0.1558880911014151</v>
       </c>
       <c r="C82">
-        <v>43.06264150157631</v>
+        <v>40.89760547585729</v>
       </c>
       <c r="D82">
-        <v>-13.2173584984237</v>
+        <v>-13.21839452414269</v>
       </c>
       <c r="E82">
-        <v>130.22</v>
+        <v>132.384</v>
       </c>
       <c r="F82">
-        <v>173.12</v>
+        <v>175.284</v>
       </c>
       <c r="G82">
         <v>229.4</v>
@@ -8011,28 +8011,28 @@
         <v>104.883</v>
       </c>
       <c r="M82">
-        <v>8.967616</v>
+        <v>9.0797112</v>
       </c>
       <c r="N82">
-        <v>95.91538400000002</v>
+        <v>95.8032888</v>
       </c>
       <c r="O82">
-        <v>9.591538400000003</v>
+        <v>9.580328880000001</v>
       </c>
       <c r="P82">
-        <v>86.32384560000001</v>
+        <v>86.22295992000001</v>
       </c>
       <c r="Q82">
-        <v>86.64084560000001</v>
+        <v>86.53995992</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5935147976784655</v>
+        <v>0.6217152163232377</v>
       </c>
       <c r="T82">
-        <v>3.34975552047751</v>
+        <v>3.522225770387679</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>11.69575057629586</v>
+        <v>11.55135859387246</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1558880911014151</v>
+        <v>0.1557772226671372</v>
       </c>
       <c r="C83">
-        <v>40.89760547585729</v>
+        <v>38.7325692877105</v>
       </c>
       <c r="D83">
-        <v>-13.21839452414269</v>
+        <v>-13.2194307122895</v>
       </c>
       <c r="E83">
-        <v>132.384</v>
+        <v>134.548</v>
       </c>
       <c r="F83">
-        <v>175.284</v>
+        <v>177.448</v>
       </c>
       <c r="G83">
         <v>229.4</v>
@@ -8093,28 +8093,28 @@
         <v>104.883</v>
       </c>
       <c r="M83">
-        <v>9.0797112</v>
+        <v>9.191806400000001</v>
       </c>
       <c r="N83">
-        <v>95.8032888</v>
+        <v>95.69119360000001</v>
       </c>
       <c r="O83">
-        <v>9.580328880000001</v>
+        <v>9.56911936</v>
       </c>
       <c r="P83">
-        <v>86.22295992000001</v>
+        <v>86.12207424</v>
       </c>
       <c r="Q83">
-        <v>86.53995992</v>
+        <v>86.43907424</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6217152163232377</v>
+        <v>0.6530490148174292</v>
       </c>
       <c r="T83">
-        <v>3.522225770387679</v>
+        <v>3.713859381398979</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>11.55135859387246</v>
+        <v>11.41048836711791</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1557772226671372</v>
+        <v>0.1556663542328593</v>
       </c>
       <c r="C84">
-        <v>38.7325692877105</v>
+        <v>36.56753293709764</v>
       </c>
       <c r="D84">
-        <v>-13.2194307122895</v>
+        <v>-13.22046706290235</v>
       </c>
       <c r="E84">
-        <v>134.548</v>
+        <v>136.712</v>
       </c>
       <c r="F84">
-        <v>177.448</v>
+        <v>179.612</v>
       </c>
       <c r="G84">
         <v>229.4</v>
@@ -8175,28 +8175,28 @@
         <v>104.883</v>
       </c>
       <c r="M84">
-        <v>9.191806400000001</v>
+        <v>9.303901600000001</v>
       </c>
       <c r="N84">
-        <v>95.69119360000001</v>
+        <v>95.57909840000001</v>
       </c>
       <c r="O84">
-        <v>9.56911936</v>
+        <v>9.557909840000001</v>
       </c>
       <c r="P84">
-        <v>86.12207424</v>
+        <v>86.02118856000001</v>
       </c>
       <c r="Q84">
-        <v>86.43907424</v>
+        <v>86.33818856000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6530490148174292</v>
+        <v>0.6880691425462313</v>
       </c>
       <c r="T84">
-        <v>3.713859381398979</v>
+        <v>3.92803812311749</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>11.41048836711791</v>
+        <v>11.27301260365866</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1556663542328593</v>
+        <v>0.1555554857985814</v>
       </c>
       <c r="C85">
-        <v>36.56753293709764</v>
+        <v>34.40249642398055</v>
       </c>
       <c r="D85">
-        <v>-13.22046706290235</v>
+        <v>-13.22150357601945</v>
       </c>
       <c r="E85">
-        <v>136.712</v>
+        <v>138.876</v>
       </c>
       <c r="F85">
-        <v>179.612</v>
+        <v>181.776</v>
       </c>
       <c r="G85">
         <v>229.4</v>
@@ -8257,28 +8257,28 @@
         <v>104.883</v>
       </c>
       <c r="M85">
-        <v>9.303901600000001</v>
+        <v>9.4159968</v>
       </c>
       <c r="N85">
-        <v>95.57909840000001</v>
+        <v>95.46700320000001</v>
       </c>
       <c r="O85">
-        <v>9.557909840000001</v>
+        <v>9.546700320000001</v>
       </c>
       <c r="P85">
-        <v>86.02118856000001</v>
+        <v>85.92030288000001</v>
       </c>
       <c r="Q85">
-        <v>86.33818856000001</v>
+        <v>86.23730288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6880691425462313</v>
+        <v>0.7274667862411338</v>
       </c>
       <c r="T85">
-        <v>3.92803812311749</v>
+        <v>4.168989207550815</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>11.27301260365866</v>
+        <v>11.13881007266273</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1555554857985814</v>
+        <v>0.1554446173643035</v>
       </c>
       <c r="C86">
-        <v>34.40249642398055</v>
+        <v>32.23745974832099</v>
       </c>
       <c r="D86">
-        <v>-13.22150357601945</v>
+        <v>-13.22254025167901</v>
       </c>
       <c r="E86">
-        <v>138.876</v>
+        <v>141.04</v>
       </c>
       <c r="F86">
-        <v>181.776</v>
+        <v>183.94</v>
       </c>
       <c r="G86">
         <v>229.4</v>
@@ -8339,28 +8339,28 @@
         <v>104.883</v>
       </c>
       <c r="M86">
-        <v>9.4159968</v>
+        <v>9.528091999999999</v>
       </c>
       <c r="N86">
-        <v>95.46700320000001</v>
+        <v>95.35490800000001</v>
       </c>
       <c r="O86">
-        <v>9.546700320000001</v>
+        <v>9.535490800000002</v>
       </c>
       <c r="P86">
-        <v>85.92030288000001</v>
+        <v>85.8194172</v>
       </c>
       <c r="Q86">
-        <v>86.23730288</v>
+        <v>86.1364172</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7274667862411334</v>
+        <v>0.7721174490953562</v>
       </c>
       <c r="T86">
-        <v>4.168989207550813</v>
+        <v>4.442067103241914</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>11.13881007266273</v>
+        <v>11.00776524827846</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1554446173643035</v>
+        <v>0.1553337489300255</v>
       </c>
       <c r="C87">
-        <v>32.23745974832099</v>
+        <v>30.07242291008072</v>
       </c>
       <c r="D87">
-        <v>-13.22254025167901</v>
+        <v>-13.22357708991927</v>
       </c>
       <c r="E87">
-        <v>141.04</v>
+        <v>143.204</v>
       </c>
       <c r="F87">
-        <v>183.94</v>
+        <v>186.104</v>
       </c>
       <c r="G87">
         <v>229.4</v>
@@ -8421,28 +8421,28 @@
         <v>104.883</v>
       </c>
       <c r="M87">
-        <v>9.528091999999999</v>
+        <v>9.6401872</v>
       </c>
       <c r="N87">
-        <v>95.35490800000001</v>
+        <v>95.24281280000001</v>
       </c>
       <c r="O87">
-        <v>9.535490800000002</v>
+        <v>9.524281280000002</v>
       </c>
       <c r="P87">
-        <v>85.8194172</v>
+        <v>85.71853152000001</v>
       </c>
       <c r="Q87">
-        <v>86.1364172</v>
+        <v>86.03553152000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7721174490953562</v>
+        <v>0.8231467780716106</v>
       </c>
       <c r="T87">
-        <v>4.442067103241914</v>
+        <v>4.754156126888887</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>11.00776524827846</v>
+        <v>10.87976797794964</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1553337489300255</v>
+        <v>0.1552228804957476</v>
       </c>
       <c r="C88">
-        <v>30.07242291008072</v>
+        <v>27.90738590922152</v>
       </c>
       <c r="D88">
-        <v>-13.22357708991927</v>
+        <v>-13.2246140907785</v>
       </c>
       <c r="E88">
-        <v>143.204</v>
+        <v>145.368</v>
       </c>
       <c r="F88">
-        <v>186.104</v>
+        <v>188.268</v>
       </c>
       <c r="G88">
         <v>229.4</v>
@@ -8503,28 +8503,28 @@
         <v>104.883</v>
       </c>
       <c r="M88">
-        <v>9.6401872</v>
+        <v>9.7522824</v>
       </c>
       <c r="N88">
-        <v>95.24281280000001</v>
+        <v>95.13071760000001</v>
       </c>
       <c r="O88">
-        <v>9.524281280000002</v>
+        <v>9.513071760000001</v>
       </c>
       <c r="P88">
-        <v>85.71853152000001</v>
+        <v>85.61764584000001</v>
       </c>
       <c r="Q88">
-        <v>86.03553152000001</v>
+        <v>85.93464584</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8231467780716106</v>
+        <v>0.8820267730442121</v>
       </c>
       <c r="T88">
-        <v>4.754156126888887</v>
+        <v>5.114258846481548</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>10.87976797794964</v>
+        <v>10.75471317360539</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1552228804957476</v>
+        <v>0.1551120120614697</v>
       </c>
       <c r="C89">
-        <v>27.90738590922152</v>
+        <v>25.74234874570504</v>
       </c>
       <c r="D89">
-        <v>-13.2246140907785</v>
+        <v>-13.22565125429494</v>
       </c>
       <c r="E89">
-        <v>145.368</v>
+        <v>147.532</v>
       </c>
       <c r="F89">
-        <v>188.268</v>
+        <v>190.432</v>
       </c>
       <c r="G89">
         <v>229.4</v>
@@ -8585,28 +8585,28 @@
         <v>104.883</v>
       </c>
       <c r="M89">
-        <v>9.7522824</v>
+        <v>9.864377600000001</v>
       </c>
       <c r="N89">
-        <v>95.13071760000001</v>
+        <v>95.01862240000001</v>
       </c>
       <c r="O89">
-        <v>9.513071760000001</v>
+        <v>9.501862240000001</v>
       </c>
       <c r="P89">
-        <v>85.61764584000001</v>
+        <v>85.51676016000002</v>
       </c>
       <c r="Q89">
-        <v>85.93464584</v>
+        <v>85.83376016000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8820267730442121</v>
+        <v>0.9507201005122472</v>
       </c>
       <c r="T89">
-        <v>5.114258846481548</v>
+        <v>5.53437868600632</v>
       </c>
       <c r="U89">
         <v>0.0518</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>10.75471317360539</v>
+        <v>10.63250052390533</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1551120120614697</v>
+        <v>0.1550011436271918</v>
       </c>
       <c r="C90">
-        <v>25.74234874570504</v>
+        <v>23.57731141949313</v>
       </c>
       <c r="D90">
-        <v>-13.22565125429494</v>
+        <v>-13.22668858050687</v>
       </c>
       <c r="E90">
-        <v>147.532</v>
+        <v>149.696</v>
       </c>
       <c r="F90">
-        <v>190.432</v>
+        <v>192.596</v>
       </c>
       <c r="G90">
         <v>229.4</v>
@@ -8667,28 +8667,28 @@
         <v>104.883</v>
       </c>
       <c r="M90">
-        <v>9.864377600000001</v>
+        <v>9.9764728</v>
       </c>
       <c r="N90">
-        <v>95.01862240000001</v>
+        <v>94.90652720000001</v>
       </c>
       <c r="O90">
-        <v>9.501862240000001</v>
+        <v>9.490652720000002</v>
       </c>
       <c r="P90">
-        <v>85.51676016000002</v>
+        <v>85.41587448000001</v>
       </c>
       <c r="Q90">
-        <v>85.83376016000001</v>
+        <v>85.73287448000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9507201005122472</v>
+        <v>1.031903123883561</v>
       </c>
       <c r="T90">
-        <v>5.53437868600632</v>
+        <v>6.030883950899232</v>
       </c>
       <c r="U90">
         <v>0.0518</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>10.63250052390533</v>
+        <v>10.51303422588392</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1550011436271918</v>
+        <v>0.1548902751929138</v>
       </c>
       <c r="C91">
-        <v>23.57731141949313</v>
+        <v>21.41227393054743</v>
       </c>
       <c r="D91">
-        <v>-13.22668858050687</v>
+        <v>-13.22772606945257</v>
       </c>
       <c r="E91">
-        <v>149.696</v>
+        <v>151.86</v>
       </c>
       <c r="F91">
-        <v>192.596</v>
+        <v>194.76</v>
       </c>
       <c r="G91">
         <v>229.4</v>
@@ -8749,28 +8749,28 @@
         <v>104.883</v>
       </c>
       <c r="M91">
-        <v>9.9764728</v>
+        <v>10.088568</v>
       </c>
       <c r="N91">
-        <v>94.90652720000001</v>
+        <v>94.79443200000001</v>
       </c>
       <c r="O91">
-        <v>9.490652720000002</v>
+        <v>9.479443200000002</v>
       </c>
       <c r="P91">
-        <v>85.41587448000001</v>
+        <v>85.31498880000001</v>
       </c>
       <c r="Q91">
-        <v>85.73287448000001</v>
+        <v>85.6319888</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.031903123883561</v>
+        <v>1.129322751929138</v>
       </c>
       <c r="T91">
-        <v>6.030883950899232</v>
+        <v>6.626690268770726</v>
       </c>
       <c r="U91">
         <v>0.0518</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>10.51303422588392</v>
+        <v>10.39622273448521</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1548902751929138</v>
+        <v>0.1547794067586359</v>
       </c>
       <c r="C92">
-        <v>21.41227393054743</v>
+        <v>19.24723627882966</v>
       </c>
       <c r="D92">
-        <v>-13.22772606945257</v>
+        <v>-13.22876372117034</v>
       </c>
       <c r="E92">
-        <v>151.86</v>
+        <v>154.024</v>
       </c>
       <c r="F92">
-        <v>194.76</v>
+        <v>196.924</v>
       </c>
       <c r="G92">
         <v>229.4</v>
@@ -8831,28 +8831,28 @@
         <v>104.883</v>
       </c>
       <c r="M92">
-        <v>10.088568</v>
+        <v>10.2006632</v>
       </c>
       <c r="N92">
-        <v>94.79443200000001</v>
+        <v>94.68233680000002</v>
       </c>
       <c r="O92">
-        <v>9.479443200000002</v>
+        <v>9.468233680000003</v>
       </c>
       <c r="P92">
-        <v>85.31498880000001</v>
+        <v>85.21410312000002</v>
       </c>
       <c r="Q92">
-        <v>85.6319888</v>
+        <v>85.53110312000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.129322751929138</v>
+        <v>1.248391186207066</v>
       </c>
       <c r="T92">
-        <v>6.626690268770726</v>
+        <v>7.354897990613664</v>
       </c>
       <c r="U92">
         <v>0.0518</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>10.39622273448521</v>
+        <v>10.28197852861175</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1547794067586359</v>
+        <v>0.154668538324358</v>
       </c>
       <c r="C93">
-        <v>19.24723627882966</v>
+        <v>17.08219846430148</v>
       </c>
       <c r="D93">
-        <v>-13.22876372117034</v>
+        <v>-13.2298015356985</v>
       </c>
       <c r="E93">
-        <v>154.024</v>
+        <v>156.188</v>
       </c>
       <c r="F93">
-        <v>196.924</v>
+        <v>199.088</v>
       </c>
       <c r="G93">
         <v>229.4</v>
@@ -8913,28 +8913,28 @@
         <v>104.883</v>
       </c>
       <c r="M93">
-        <v>10.2006632</v>
+        <v>10.3127584</v>
       </c>
       <c r="N93">
-        <v>94.68233680000002</v>
+        <v>94.5702416</v>
       </c>
       <c r="O93">
-        <v>9.468233680000003</v>
+        <v>9.457024160000001</v>
       </c>
       <c r="P93">
-        <v>85.21410312000002</v>
+        <v>85.11321744</v>
       </c>
       <c r="Q93">
-        <v>85.53110312000001</v>
+        <v>85.43021743999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.248391186207066</v>
+        <v>1.397226729054475</v>
       </c>
       <c r="T93">
-        <v>7.354897990613664</v>
+        <v>8.265157642917337</v>
       </c>
       <c r="U93">
         <v>0.0518</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>10.28197852861175</v>
+        <v>10.17021789243118</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.154668538324358</v>
+        <v>0.15455766989008</v>
       </c>
       <c r="C94">
-        <v>17.08219846430148</v>
+        <v>14.91716048692464</v>
       </c>
       <c r="D94">
-        <v>-13.2298015356985</v>
+        <v>-13.23083951307536</v>
       </c>
       <c r="E94">
-        <v>156.188</v>
+        <v>158.352</v>
       </c>
       <c r="F94">
-        <v>199.088</v>
+        <v>201.252</v>
       </c>
       <c r="G94">
         <v>229.4</v>
@@ -8995,28 +8995,28 @@
         <v>104.883</v>
       </c>
       <c r="M94">
-        <v>10.3127584</v>
+        <v>10.4248536</v>
       </c>
       <c r="N94">
-        <v>94.5702416</v>
+        <v>94.4581464</v>
       </c>
       <c r="O94">
-        <v>9.457024160000001</v>
+        <v>9.44581464</v>
       </c>
       <c r="P94">
-        <v>85.11321744</v>
+        <v>85.01233176000001</v>
       </c>
       <c r="Q94">
-        <v>85.43021743999999</v>
+        <v>85.32933176</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.397226729054475</v>
+        <v>1.58858671271543</v>
       </c>
       <c r="T94">
-        <v>8.265157642917337</v>
+        <v>9.435491481593488</v>
       </c>
       <c r="U94">
         <v>0.0518</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>10.17021789243118</v>
+        <v>10.06086071079214</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.15455766989008</v>
+        <v>0.1544468014558021</v>
       </c>
       <c r="C95">
-        <v>14.91716048692464</v>
+        <v>12.75212234666074</v>
       </c>
       <c r="D95">
-        <v>-13.23083951307536</v>
+        <v>-13.23187765333925</v>
       </c>
       <c r="E95">
-        <v>158.352</v>
+        <v>160.516</v>
       </c>
       <c r="F95">
-        <v>201.252</v>
+        <v>203.416</v>
       </c>
       <c r="G95">
         <v>229.4</v>
@@ -9077,28 +9077,28 @@
         <v>104.883</v>
       </c>
       <c r="M95">
-        <v>10.4248536</v>
+        <v>10.5369488</v>
       </c>
       <c r="N95">
-        <v>94.4581464</v>
+        <v>94.34605120000001</v>
       </c>
       <c r="O95">
-        <v>9.44581464</v>
+        <v>9.434605120000001</v>
       </c>
       <c r="P95">
-        <v>85.01233176000001</v>
+        <v>84.91144608</v>
       </c>
       <c r="Q95">
-        <v>85.32933176</v>
+        <v>85.22844608</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.58858671271543</v>
+        <v>1.843733357596703</v>
       </c>
       <c r="T95">
-        <v>9.435491481593488</v>
+        <v>10.99593659982836</v>
       </c>
       <c r="U95">
         <v>0.0518</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>10.06086071079214</v>
+        <v>9.953830277698605</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1544468014558021</v>
+        <v>0.1543359330215242</v>
       </c>
       <c r="C96">
-        <v>12.75212234666074</v>
+        <v>10.58708404347146</v>
       </c>
       <c r="D96">
-        <v>-13.23187765333925</v>
+        <v>-13.23291595652852</v>
       </c>
       <c r="E96">
-        <v>160.516</v>
+        <v>162.68</v>
       </c>
       <c r="F96">
-        <v>203.416</v>
+        <v>205.58</v>
       </c>
       <c r="G96">
         <v>229.4</v>
@@ -9159,28 +9159,28 @@
         <v>104.883</v>
       </c>
       <c r="M96">
-        <v>10.5369488</v>
+        <v>10.649044</v>
       </c>
       <c r="N96">
-        <v>94.34605120000001</v>
+        <v>94.23395600000001</v>
       </c>
       <c r="O96">
-        <v>9.434605120000001</v>
+        <v>9.423395600000001</v>
       </c>
       <c r="P96">
-        <v>84.91144608</v>
+        <v>84.8105604</v>
       </c>
       <c r="Q96">
-        <v>85.22844608</v>
+        <v>85.12756039999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.843733357596703</v>
+        <v>2.200938660430486</v>
       </c>
       <c r="T96">
-        <v>10.99593659982836</v>
+        <v>13.18055976535718</v>
       </c>
       <c r="U96">
         <v>0.0518</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>9.953830277698605</v>
+        <v>9.849053116880727</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1543359330215242</v>
+        <v>0.1556938645872462</v>
       </c>
       <c r="C97">
-        <v>10.58708404347146</v>
+        <v>8.435790107258583</v>
       </c>
       <c r="D97">
-        <v>-13.23291595652852</v>
+        <v>-13.22020989274139</v>
       </c>
       <c r="E97">
-        <v>162.68</v>
+        <v>164.844</v>
       </c>
       <c r="F97">
-        <v>205.58</v>
+        <v>207.744</v>
       </c>
       <c r="G97">
         <v>229.4</v>
@@ -9241,45 +9241,45 @@
         <v>104.883</v>
       </c>
       <c r="M97">
-        <v>10.649044</v>
+        <v>11.114304</v>
       </c>
       <c r="N97">
-        <v>94.23395600000001</v>
+        <v>93.76869600000001</v>
       </c>
       <c r="O97">
-        <v>9.423395600000001</v>
+        <v>9.376869600000001</v>
       </c>
       <c r="P97">
-        <v>84.8105604</v>
+        <v>84.3918264</v>
       </c>
       <c r="Q97">
-        <v>85.12756039999999</v>
+        <v>84.70882639999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.200938660430486</v>
+        <v>2.736746614681161</v>
       </c>
       <c r="T97">
-        <v>13.18055976535718</v>
+        <v>16.4574945136504</v>
       </c>
       <c r="U97">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V97">
         <v>0.1</v>
       </c>
       <c r="W97">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y97">
-        <v>9.849053116880727</v>
+        <v>9.436758253148374</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1556938645872462</v>
+        <v>0.1555982961529683</v>
       </c>
       <c r="C98">
-        <v>8.435790107258612</v>
+        <v>6.270896678838596</v>
       </c>
       <c r="D98">
-        <v>-13.22020989274139</v>
+        <v>-13.22110332116141</v>
       </c>
       <c r="E98">
-        <v>164.844</v>
+        <v>167.008</v>
       </c>
       <c r="F98">
-        <v>207.744</v>
+        <v>209.908</v>
       </c>
       <c r="G98">
         <v>229.4</v>
@@ -9323,28 +9323,28 @@
         <v>104.883</v>
       </c>
       <c r="M98">
-        <v>11.114304</v>
+        <v>11.230078</v>
       </c>
       <c r="N98">
-        <v>93.76869600000001</v>
+        <v>93.65292200000002</v>
       </c>
       <c r="O98">
-        <v>9.376869600000001</v>
+        <v>9.365292200000003</v>
       </c>
       <c r="P98">
-        <v>84.3918264</v>
+        <v>84.28762980000002</v>
       </c>
       <c r="Q98">
-        <v>84.70882639999999</v>
+        <v>84.60462980000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.736746614681153</v>
+        <v>3.629759871765607</v>
       </c>
       <c r="T98">
-        <v>16.45749451365036</v>
+        <v>21.91905242747238</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>9.436758253148374</v>
+        <v>9.339472085590147</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1555982961529683</v>
+        <v>0.1555027277186904</v>
       </c>
       <c r="C99">
-        <v>6.270896678838596</v>
+        <v>4.106003129653715</v>
       </c>
       <c r="D99">
-        <v>-13.22110332116141</v>
+        <v>-13.22199687034628</v>
       </c>
       <c r="E99">
-        <v>167.008</v>
+        <v>169.172</v>
       </c>
       <c r="F99">
-        <v>209.908</v>
+        <v>212.072</v>
       </c>
       <c r="G99">
         <v>229.4</v>
@@ -9405,28 +9405,28 @@
         <v>104.883</v>
       </c>
       <c r="M99">
-        <v>11.230078</v>
+        <v>11.345852</v>
       </c>
       <c r="N99">
-        <v>93.65292200000002</v>
+        <v>93.537148</v>
       </c>
       <c r="O99">
-        <v>9.365292200000003</v>
+        <v>9.353714800000001</v>
       </c>
       <c r="P99">
-        <v>84.28762980000002</v>
+        <v>84.1834332</v>
       </c>
       <c r="Q99">
-        <v>84.60462980000001</v>
+        <v>84.50043319999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.629759871765607</v>
+        <v>5.415786385934515</v>
       </c>
       <c r="T99">
-        <v>21.91905242747238</v>
+        <v>32.84216825511643</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>9.339472085590147</v>
+        <v>9.244171350022897</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1555027277186904</v>
+        <v>0.1554071592844125</v>
       </c>
       <c r="C100">
-        <v>4.106003129653715</v>
+        <v>1.941109459679552</v>
       </c>
       <c r="D100">
-        <v>-13.22199687034628</v>
+        <v>-13.22289054032047</v>
       </c>
       <c r="E100">
-        <v>169.172</v>
+        <v>171.336</v>
       </c>
       <c r="F100">
-        <v>212.072</v>
+        <v>214.236</v>
       </c>
       <c r="G100">
         <v>229.4</v>
@@ -9487,28 +9487,28 @@
         <v>104.883</v>
       </c>
       <c r="M100">
-        <v>11.345852</v>
+        <v>11.461626</v>
       </c>
       <c r="N100">
-        <v>93.537148</v>
+        <v>93.42137400000001</v>
       </c>
       <c r="O100">
-        <v>9.353714800000001</v>
+        <v>9.342137400000002</v>
       </c>
       <c r="P100">
-        <v>84.1834332</v>
+        <v>84.07923660000002</v>
       </c>
       <c r="Q100">
-        <v>84.50043319999999</v>
+        <v>84.39623660000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.415786385934515</v>
+        <v>10.77386592844124</v>
       </c>
       <c r="T100">
-        <v>32.84216825511643</v>
+        <v>65.61151573804855</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>9.244171350022897</v>
+        <v>9.150795881840851</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1554071592844125</v>
-      </c>
-      <c r="C101">
-        <v>1.941109459679552</v>
-      </c>
-      <c r="D101">
-        <v>-13.22289054032047</v>
-      </c>
-      <c r="E101">
-        <v>171.336</v>
-      </c>
-      <c r="F101">
-        <v>214.236</v>
-      </c>
-      <c r="G101">
-        <v>229.4</v>
-      </c>
-      <c r="H101">
-        <v>173.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>105.2</v>
-      </c>
-      <c r="K101">
-        <v>0.317</v>
-      </c>
-      <c r="L101">
-        <v>104.883</v>
-      </c>
-      <c r="M101">
-        <v>11.461626</v>
-      </c>
-      <c r="N101">
-        <v>93.42137400000001</v>
-      </c>
-      <c r="O101">
-        <v>9.342137400000002</v>
-      </c>
-      <c r="P101">
-        <v>84.07923660000002</v>
-      </c>
-      <c r="Q101">
-        <v>84.39623660000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.77386592844124</v>
-      </c>
-      <c r="T101">
-        <v>65.61151573804855</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.1</v>
-      </c>
-      <c r="W101">
-        <v>0.04815</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>9.150795881840851</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
